--- a/docs/egg-invoice-reconciliation-2026-10-16.xlsx
+++ b/docs/egg-invoice-reconciliation-2026-10-16.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Invoices" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Invoices'!$A$1:$J$472</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Invoices'!$A$1:$J$473</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>94325960</v>
+        <v>94052960</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>72884305</v>
+        <v>73157305</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>10288807</v>
+        <v>10561807</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>180807147</v>
+        <v>181080147</v>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J472"/>
+  <dimension ref="A1:J473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10347,50 +10347,42 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B226" s="5" t="inlineStr">
+      <c r="A226" s="8" t="inlineStr">
+        <is>
+          <t>Only in Zoho - import</t>
+        </is>
+      </c>
+      <c r="B226" s="8" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0791</t>
         </is>
       </c>
-      <c r="C226" s="5" t="inlineStr">
+      <c r="C226" s="8" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="D226" s="5" t="inlineStr">
+      <c r="D226" s="8" t="inlineStr">
         <is>
           <t>Tapan Saha</t>
         </is>
       </c>
-      <c r="E226" s="6" t="n">
+      <c r="E226" s="9" t="n">
         <v>273000</v>
       </c>
-      <c r="F226" s="5" t="inlineStr">
+      <c r="F226" s="8" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0788</t>
         </is>
       </c>
-      <c r="G226" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0779</t>
-        </is>
-      </c>
-      <c r="H226" s="5" t="inlineStr"/>
-      <c r="I226" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J226" s="7" t="inlineStr">
-        <is>
-          <t>Zoho's date is the dispatch day</t>
-        </is>
-      </c>
+      <c r="G226" s="8" t="inlineStr"/>
+      <c r="H226" s="8" t="inlineStr"/>
+      <c r="I226" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J226" s="10" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
@@ -11200,7 +11192,7 @@
       </c>
       <c r="D245" s="11" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E245" s="12" t="n">
@@ -11209,7 +11201,7 @@
       <c r="F245" s="11" t="inlineStr"/>
       <c r="G245" s="11" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0783</t>
+          <t>A-INV-EG-27-0779</t>
         </is>
       </c>
       <c r="H245" s="11" t="inlineStr"/>
@@ -11221,46 +11213,42 @@
       <c r="J245" s="13" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B246" s="5" t="inlineStr">
+      <c r="A246" s="11" t="inlineStr">
+        <is>
+          <t>Only in niko - keep</t>
+        </is>
+      </c>
+      <c r="B246" s="11" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0811</t>
         </is>
       </c>
-      <c r="C246" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D246" s="5" t="inlineStr">
-        <is>
-          <t>SS Food</t>
-        </is>
-      </c>
-      <c r="E246" s="6" t="n">
-        <v>188650</v>
-      </c>
-      <c r="F246" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0798</t>
-        </is>
-      </c>
-      <c r="G246" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0798</t>
-        </is>
-      </c>
-      <c r="H246" s="5" t="inlineStr"/>
-      <c r="I246" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J246" s="7" t="inlineStr"/>
+      <c r="C246" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D246" s="11" t="inlineStr">
+        <is>
+          <t>Kamakhya Traders</t>
+        </is>
+      </c>
+      <c r="E246" s="12" t="n">
+        <v>273000</v>
+      </c>
+      <c r="F246" s="11" t="inlineStr"/>
+      <c r="G246" s="11" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0783</t>
+        </is>
+      </c>
+      <c r="H246" s="11" t="inlineStr"/>
+      <c r="I246" s="11" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J246" s="13" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
@@ -11280,20 +11268,20 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Protein Shop</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E247" s="6" t="n">
-        <v>150150</v>
+        <v>188650</v>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0799</t>
+          <t>A-INV-EG-27-0798</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0799</t>
+          <t>A-INV-EG-27-0798</t>
         </is>
       </c>
       <c r="H247" s="5" t="inlineStr"/>
@@ -11322,20 +11310,20 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Protein Shop</t>
         </is>
       </c>
       <c r="E248" s="6" t="n">
-        <v>407200</v>
+        <v>150150</v>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0800</t>
+          <t>A-INV-EG-27-0799</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0800</t>
+          <t>A-INV-EG-27-0799</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr"/>
@@ -11364,20 +11352,20 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>DN Store</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E249" s="6" t="n">
-        <v>278250</v>
+        <v>407200</v>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0802</t>
+          <t>A-INV-EG-27-0800</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0802</t>
+          <t>A-INV-EG-27-0800</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr"/>
@@ -11406,20 +11394,20 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>M/s Mayengbam Enterprises</t>
+          <t>DN Store</t>
         </is>
       </c>
       <c r="E250" s="6" t="n">
-        <v>1184691</v>
+        <v>278250</v>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0803</t>
+          <t>A-INV-EG-27-0802</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0803</t>
+          <t>A-INV-EG-27-0802</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr"/>
@@ -11448,20 +11436,20 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>M/s Mayengbam Enterprises</t>
         </is>
       </c>
       <c r="E251" s="6" t="n">
-        <v>273000</v>
+        <v>1184691</v>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0809</t>
+          <t>A-INV-EG-27-0803</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0809</t>
+          <t>A-INV-EG-27-0803</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr"/>
@@ -11470,11 +11458,7 @@
           <t>paid</t>
         </is>
       </c>
-      <c r="J251" s="7" t="inlineStr">
-        <is>
-          <t>Zoho's date is the dispatch day</t>
-        </is>
-      </c>
+      <c r="J251" s="7" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
@@ -11489,25 +11473,25 @@
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Chowdhury n Sons</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E252" s="6" t="n">
-        <v>1110150</v>
+        <v>273000</v>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0804</t>
+          <t>A-INV-EG-27-0809</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0812</t>
+          <t>A-INV-EG-27-0809</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr"/>
@@ -11516,7 +11500,11 @@
           <t>paid</t>
         </is>
       </c>
-      <c r="J252" s="7" t="inlineStr"/>
+      <c r="J252" s="7" t="inlineStr">
+        <is>
+          <t>Zoho's date is the dispatch day</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
@@ -11536,20 +11524,20 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Chowdhury n Sons</t>
         </is>
       </c>
       <c r="E253" s="6" t="n">
-        <v>518700</v>
+        <v>1110150</v>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0805</t>
+          <t>A-INV-EG-27-0804</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0806</t>
+          <t>A-INV-EG-27-0812</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr"/>
@@ -11578,20 +11566,20 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Josef Ali</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E254" s="6" t="n">
-        <v>149000</v>
+        <v>518700</v>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0832</t>
+          <t>A-INV-EG-27-0805</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0811</t>
+          <t>A-INV-EG-27-0806</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr"/>
@@ -11620,20 +11608,20 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Josef Ali</t>
         </is>
       </c>
       <c r="E255" s="6" t="n">
-        <v>535400</v>
+        <v>149000</v>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0833</t>
+          <t>A-INV-EG-27-0832</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0810</t>
+          <t>A-INV-EG-27-0811</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr"/>
@@ -11662,20 +11650,20 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E256" s="6" t="n">
-        <v>273000</v>
+        <v>535400</v>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0835</t>
+          <t>A-INV-EG-27-0833</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0801</t>
+          <t>A-INV-EG-27-0810</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr"/>
@@ -11684,11 +11672,7 @@
           <t>paid</t>
         </is>
       </c>
-      <c r="J256" s="7" t="inlineStr">
-        <is>
-          <t>Zoho's date is the dispatch day</t>
-        </is>
-      </c>
+      <c r="J256" s="7" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
@@ -11708,20 +11692,20 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Surjya Store</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E257" s="6" t="n">
-        <v>284350</v>
+        <v>273000</v>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>INV-2026-27/0288</t>
+          <t>A-INV-EG-27-0835</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0808</t>
+          <t>A-INV-EG-27-0801</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr"/>
@@ -11730,167 +11714,171 @@
           <t>paid</t>
         </is>
       </c>
-      <c r="J257" s="7" t="inlineStr"/>
+      <c r="J257" s="7" t="inlineStr">
+        <is>
+          <t>Zoho's date is the dispatch day</t>
+        </is>
+      </c>
     </row>
     <row r="258">
-      <c r="A258" s="8" t="inlineStr">
+      <c r="A258" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B258" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0823</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>Surjya Store</t>
+        </is>
+      </c>
+      <c r="E258" s="6" t="n">
+        <v>284350</v>
+      </c>
+      <c r="F258" s="5" t="inlineStr">
+        <is>
+          <t>INV-2026-27/0288</t>
+        </is>
+      </c>
+      <c r="G258" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0808</t>
+        </is>
+      </c>
+      <c r="H258" s="5" t="inlineStr"/>
+      <c r="I258" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J258" s="7" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="8" t="inlineStr">
         <is>
           <t>Only in Zoho - import</t>
         </is>
       </c>
-      <c r="B258" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0823</t>
-        </is>
-      </c>
-      <c r="C258" s="8" t="inlineStr">
+      <c r="B259" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0824</t>
+        </is>
+      </c>
+      <c r="C259" s="8" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D258" s="8" t="inlineStr">
+      <c r="D259" s="8" t="inlineStr">
         <is>
           <t>Zakir Egg Store</t>
         </is>
       </c>
-      <c r="E258" s="9" t="n">
+      <c r="E259" s="9" t="n">
         <v>1074900</v>
       </c>
-      <c r="F258" s="8" t="inlineStr">
+      <c r="F259" s="8" t="inlineStr">
         <is>
           <t>INV-2026-27/0289</t>
         </is>
       </c>
-      <c r="G258" s="8" t="inlineStr"/>
-      <c r="H258" s="8" t="inlineStr"/>
-      <c r="I258" s="8" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J258" s="10" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B259" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0824</t>
-        </is>
-      </c>
-      <c r="C259" s="5" t="inlineStr">
+      <c r="G259" s="8" t="inlineStr"/>
+      <c r="H259" s="8" t="inlineStr"/>
+      <c r="I259" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J259" s="10" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0825</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D259" s="5" t="inlineStr">
+      <c r="D260" s="5" t="inlineStr">
         <is>
           <t>Sahil Egg Center</t>
         </is>
       </c>
-      <c r="E259" s="6" t="n">
+      <c r="E260" s="6" t="n">
         <v>602500</v>
       </c>
-      <c r="F259" s="5" t="inlineStr">
+      <c r="F260" s="5" t="inlineStr">
         <is>
           <t>INV-2026-27/0290</t>
         </is>
       </c>
-      <c r="G259" s="5" t="inlineStr">
+      <c r="G260" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0813</t>
         </is>
       </c>
-      <c r="H259" s="5" t="inlineStr"/>
-      <c r="I259" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J259" s="7" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="11" t="inlineStr">
+      <c r="H260" s="5" t="inlineStr"/>
+      <c r="I260" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J260" s="7" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="11" t="inlineStr">
         <is>
           <t>Only in niko - keep</t>
         </is>
       </c>
-      <c r="B260" s="11" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0825</t>
-        </is>
-      </c>
-      <c r="C260" s="11" t="inlineStr">
+      <c r="B261" s="11" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0826</t>
+        </is>
+      </c>
+      <c r="C261" s="11" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D260" s="11" t="inlineStr">
+      <c r="D261" s="11" t="inlineStr">
         <is>
           <t>Zakir Egg Store</t>
         </is>
       </c>
-      <c r="E260" s="12" t="n">
+      <c r="E261" s="12" t="n">
         <v>1274650</v>
       </c>
-      <c r="F260" s="11" t="inlineStr"/>
-      <c r="G260" s="11" t="inlineStr">
+      <c r="F261" s="11" t="inlineStr"/>
+      <c r="G261" s="11" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0807</t>
         </is>
       </c>
-      <c r="H260" s="11" t="inlineStr"/>
-      <c r="I260" s="11" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J260" s="13" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B261" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0826</t>
-        </is>
-      </c>
-      <c r="C261" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="D261" s="5" t="inlineStr">
-        <is>
-          <t>PD Egg Store</t>
-        </is>
-      </c>
-      <c r="E261" s="6" t="n">
-        <v>277100</v>
-      </c>
-      <c r="F261" s="5" t="inlineStr">
-        <is>
-          <t>INV-2026-27/0291</t>
-        </is>
-      </c>
-      <c r="G261" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0814</t>
-        </is>
-      </c>
-      <c r="H261" s="5" t="inlineStr"/>
-      <c r="I261" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J261" s="7" t="inlineStr"/>
+      <c r="H261" s="11" t="inlineStr"/>
+      <c r="I261" s="11" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J261" s="13" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
@@ -11910,20 +11898,20 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>PD Egg Store</t>
         </is>
       </c>
       <c r="E262" s="6" t="n">
-        <v>273000</v>
+        <v>277100</v>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>INV-2026-27/0292</t>
+          <t>INV-2026-27/0291</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0815</t>
+          <t>A-INV-EG-27-0814</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr"/>
@@ -11952,20 +11940,20 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>Rahman Store</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E263" s="6" t="n">
-        <v>573000</v>
+        <v>273000</v>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>INV-2026-27/0293</t>
+          <t>INV-2026-27/0292</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0816</t>
+          <t>A-INV-EG-27-0815</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr"/>
@@ -11994,20 +11982,20 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>Fariha Store</t>
+          <t>Rahman Store</t>
         </is>
       </c>
       <c r="E264" s="6" t="n">
-        <v>229750</v>
+        <v>573000</v>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>INV-2026-27/0294</t>
+          <t>INV-2026-27/0293</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0817</t>
+          <t>A-INV-EG-27-0816</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr"/>
@@ -12031,25 +12019,25 @@
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>Fariha Store</t>
         </is>
       </c>
       <c r="E265" s="6" t="n">
-        <v>412650</v>
+        <v>229750</v>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>INV-2026-27/0295</t>
+          <t>INV-2026-27/0294</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0818</t>
+          <t>A-INV-EG-27-0817</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr"/>
@@ -12078,20 +12066,20 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>DG Egg Point (Debajeet Gogoi)</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E266" s="6" t="n">
-        <v>233835</v>
+        <v>412650</v>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>INV-2026-27/0296</t>
+          <t>INV-2026-27/0295</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0819</t>
+          <t>A-INV-EG-27-0818</t>
         </is>
       </c>
       <c r="H266" s="5" t="inlineStr"/>
@@ -12120,20 +12108,20 @@
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>DD Egg Point (Gahin Handique)</t>
+          <t>DG Egg Point (Debajeet Gogoi)</t>
         </is>
       </c>
       <c r="E267" s="6" t="n">
-        <v>308231</v>
+        <v>233835</v>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>INV-2026-27/0297</t>
+          <t>INV-2026-27/0296</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0820</t>
+          <t>A-INV-EG-27-0819</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr"/>
@@ -12145,84 +12133,84 @@
       <c r="J267" s="7" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="8" t="inlineStr">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0833</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>DD Egg Point (Gahin Handique)</t>
+        </is>
+      </c>
+      <c r="E268" s="6" t="n">
+        <v>308231</v>
+      </c>
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>INV-2026-27/0297</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0820</t>
+        </is>
+      </c>
+      <c r="H268" s="5" t="inlineStr"/>
+      <c r="I268" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J268" s="7" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="8" t="inlineStr">
         <is>
           <t>Only in Zoho - import</t>
         </is>
       </c>
-      <c r="B268" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0833</t>
-        </is>
-      </c>
-      <c r="C268" s="8" t="inlineStr">
+      <c r="B269" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0834</t>
+        </is>
+      </c>
+      <c r="C269" s="8" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="D268" s="8" t="inlineStr">
+      <c r="D269" s="8" t="inlineStr">
         <is>
           <t>Kamakhya Traders</t>
         </is>
       </c>
-      <c r="E268" s="9" t="n">
+      <c r="E269" s="9" t="n">
         <v>275100</v>
       </c>
-      <c r="F268" s="8" t="inlineStr">
+      <c r="F269" s="8" t="inlineStr">
         <is>
           <t>INV-2026-27/0298</t>
         </is>
       </c>
-      <c r="G268" s="8" t="inlineStr"/>
-      <c r="H268" s="8" t="inlineStr"/>
-      <c r="I268" s="8" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J268" s="10" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0834</t>
-        </is>
-      </c>
-      <c r="C269" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
-        <is>
-          <t>NB Traders</t>
-        </is>
-      </c>
-      <c r="E269" s="6" t="n">
-        <v>539600</v>
-      </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>INV-2026-27/0299</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0826</t>
-        </is>
-      </c>
-      <c r="H269" s="5" t="inlineStr"/>
-      <c r="I269" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J269" s="7" t="inlineStr"/>
+      <c r="G269" s="8" t="inlineStr"/>
+      <c r="H269" s="8" t="inlineStr"/>
+      <c r="I269" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J269" s="10" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
@@ -12242,20 +12230,20 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Sayedur Rahman</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E270" s="6" t="n">
-        <v>275100</v>
+        <v>539600</v>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>INV-2026-27/0300</t>
+          <t>INV-2026-27/0299</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0822</t>
+          <t>A-INV-EG-27-0826</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr"/>
@@ -12284,20 +12272,20 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Protein Shop</t>
+          <t>Sayedur Rahman</t>
         </is>
       </c>
       <c r="E271" s="6" t="n">
-        <v>151305</v>
+        <v>275100</v>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>INV-2026-27/0301</t>
+          <t>INV-2026-27/0300</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0823</t>
+          <t>A-INV-EG-27-0822</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr"/>
@@ -12309,42 +12297,46 @@
       <c r="J271" s="7" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="8" t="inlineStr">
-        <is>
-          <t>Only in Zoho - import</t>
-        </is>
-      </c>
-      <c r="B272" s="8" t="inlineStr">
+      <c r="A272" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B272" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0837</t>
         </is>
       </c>
-      <c r="C272" s="8" t="inlineStr">
+      <c r="C272" s="5" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="D272" s="8" t="inlineStr">
-        <is>
-          <t>Kamakhya Traders</t>
-        </is>
-      </c>
-      <c r="E272" s="9" t="n">
-        <v>275100</v>
-      </c>
-      <c r="F272" s="8" t="inlineStr">
-        <is>
-          <t>INV-2026-27/0302</t>
-        </is>
-      </c>
-      <c r="G272" s="8" t="inlineStr"/>
-      <c r="H272" s="8" t="inlineStr"/>
-      <c r="I272" s="8" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J272" s="10" t="inlineStr"/>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>Protein Shop</t>
+        </is>
+      </c>
+      <c r="E272" s="6" t="n">
+        <v>151305</v>
+      </c>
+      <c r="F272" s="5" t="inlineStr">
+        <is>
+          <t>INV-2026-27/0301</t>
+        </is>
+      </c>
+      <c r="G272" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0823</t>
+        </is>
+      </c>
+      <c r="H272" s="5" t="inlineStr"/>
+      <c r="I272" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J272" s="7" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="8" t="inlineStr">
@@ -12364,15 +12356,15 @@
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Fresh Egg Traders</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E273" s="9" t="n">
-        <v>1166033</v>
+        <v>275100</v>
       </c>
       <c r="F273" s="8" t="inlineStr">
         <is>
-          <t>INV-2026-27/0303</t>
+          <t>INV-2026-27/0302</t>
         </is>
       </c>
       <c r="G273" s="8" t="inlineStr"/>
@@ -12385,122 +12377,122 @@
       <c r="J273" s="10" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B274" s="5" t="inlineStr">
+      <c r="A274" s="8" t="inlineStr">
+        <is>
+          <t>Only in Zoho - import</t>
+        </is>
+      </c>
+      <c r="B274" s="8" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0839</t>
         </is>
       </c>
-      <c r="C274" s="5" t="inlineStr">
+      <c r="C274" s="8" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="D274" s="5" t="inlineStr">
+      <c r="D274" s="8" t="inlineStr">
+        <is>
+          <t>Fresh Egg Traders</t>
+        </is>
+      </c>
+      <c r="E274" s="9" t="n">
+        <v>1166033</v>
+      </c>
+      <c r="F274" s="8" t="inlineStr">
+        <is>
+          <t>INV-2026-27/0303</t>
+        </is>
+      </c>
+      <c r="G274" s="8" t="inlineStr"/>
+      <c r="H274" s="8" t="inlineStr"/>
+      <c r="I274" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J274" s="10" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0840</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
         <is>
           <t>Surjya Store</t>
         </is>
       </c>
-      <c r="E274" s="6" t="n">
+      <c r="E275" s="6" t="n">
         <v>275100</v>
       </c>
-      <c r="F274" s="5" t="inlineStr">
+      <c r="F275" s="5" t="inlineStr">
         <is>
           <t>INV-2026-27/0304</t>
         </is>
       </c>
-      <c r="G274" s="5" t="inlineStr">
+      <c r="G275" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0824</t>
         </is>
       </c>
-      <c r="H274" s="5" t="inlineStr"/>
-      <c r="I274" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J274" s="7" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="8" t="inlineStr">
+      <c r="H275" s="5" t="inlineStr"/>
+      <c r="I275" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J275" s="7" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="8" t="inlineStr">
         <is>
           <t>Only in Zoho - import</t>
         </is>
       </c>
-      <c r="B275" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0840</t>
-        </is>
-      </c>
-      <c r="C275" s="8" t="inlineStr">
+      <c r="B276" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0841</t>
+        </is>
+      </c>
+      <c r="C276" s="8" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="D275" s="8" t="inlineStr">
+      <c r="D276" s="8" t="inlineStr">
         <is>
           <t>Sahil Egg Center</t>
         </is>
       </c>
-      <c r="E275" s="9" t="n">
+      <c r="E276" s="9" t="n">
         <v>590330</v>
       </c>
-      <c r="F275" s="8" t="inlineStr">
+      <c r="F276" s="8" t="inlineStr">
         <is>
           <t>INV-2026-27/0305</t>
         </is>
       </c>
-      <c r="G275" s="8" t="inlineStr"/>
-      <c r="H275" s="8" t="inlineStr"/>
-      <c r="I275" s="8" t="inlineStr">
+      <c r="G276" s="8" t="inlineStr"/>
+      <c r="H276" s="8" t="inlineStr"/>
+      <c r="I276" s="8" t="inlineStr">
         <is>
           <t>overdue</t>
         </is>
       </c>
-      <c r="J275" s="10" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="11" t="inlineStr">
-        <is>
-          <t>Only in niko - keep</t>
-        </is>
-      </c>
-      <c r="B276" s="11" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0841</t>
-        </is>
-      </c>
-      <c r="C276" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="D276" s="11" t="inlineStr">
-        <is>
-          <t>Kamakhya Traders</t>
-        </is>
-      </c>
-      <c r="E276" s="12" t="n">
-        <v>550200</v>
-      </c>
-      <c r="F276" s="11" t="inlineStr"/>
-      <c r="G276" s="11" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0821</t>
-        </is>
-      </c>
-      <c r="H276" s="11" t="inlineStr"/>
-      <c r="I276" s="11" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J276" s="13" t="inlineStr"/>
+      <c r="J276" s="10" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
@@ -12520,16 +12512,16 @@
       </c>
       <c r="D277" s="11" t="inlineStr">
         <is>
-          <t>Sahil Egg Center</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E277" s="12" t="n">
-        <v>602380</v>
+        <v>550200</v>
       </c>
       <c r="F277" s="11" t="inlineStr"/>
       <c r="G277" s="11" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0825</t>
+          <t>A-INV-EG-27-0821</t>
         </is>
       </c>
       <c r="H277" s="11" t="inlineStr"/>
@@ -12541,84 +12533,84 @@
       <c r="J277" s="13" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B278" s="5" t="inlineStr">
+      <c r="A278" s="11" t="inlineStr">
+        <is>
+          <t>Only in niko - keep</t>
+        </is>
+      </c>
+      <c r="B278" s="11" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0843</t>
         </is>
       </c>
-      <c r="C278" s="5" t="inlineStr">
+      <c r="C278" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D278" s="11" t="inlineStr">
+        <is>
+          <t>Sahil Egg Center</t>
+        </is>
+      </c>
+      <c r="E278" s="12" t="n">
+        <v>602380</v>
+      </c>
+      <c r="F278" s="11" t="inlineStr"/>
+      <c r="G278" s="11" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0825</t>
+        </is>
+      </c>
+      <c r="H278" s="11" t="inlineStr"/>
+      <c r="I278" s="11" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J278" s="13" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0844</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="D278" s="5" t="inlineStr">
+      <c r="D279" s="5" t="inlineStr">
         <is>
           <t>Tapan Saha</t>
         </is>
       </c>
-      <c r="E278" s="6" t="n">
+      <c r="E279" s="6" t="n">
         <v>275100</v>
       </c>
-      <c r="F278" s="5" t="inlineStr">
+      <c r="F279" s="5" t="inlineStr">
         <is>
           <t>INV-2026-27/0306</t>
         </is>
       </c>
-      <c r="G278" s="5" t="inlineStr">
+      <c r="G279" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0830</t>
         </is>
       </c>
-      <c r="H278" s="5" t="inlineStr"/>
-      <c r="I278" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J278" s="7" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="8" t="inlineStr">
-        <is>
-          <t>Only in Zoho - import</t>
-        </is>
-      </c>
-      <c r="B279" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0844</t>
-        </is>
-      </c>
-      <c r="C279" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="D279" s="8" t="inlineStr">
-        <is>
-          <t>HKD Egg Traders</t>
-        </is>
-      </c>
-      <c r="E279" s="9" t="n">
-        <v>271603</v>
-      </c>
-      <c r="F279" s="8" t="inlineStr">
-        <is>
-          <t>INV-2026-27/0307</t>
-        </is>
-      </c>
-      <c r="G279" s="8" t="inlineStr"/>
-      <c r="H279" s="8" t="inlineStr"/>
-      <c r="I279" s="8" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J279" s="10" t="inlineStr"/>
+      <c r="H279" s="5" t="inlineStr"/>
+      <c r="I279" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J279" s="7" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="8" t="inlineStr">
@@ -12638,15 +12630,15 @@
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>HKD Egg Traders</t>
         </is>
       </c>
       <c r="E280" s="9" t="n">
-        <v>275100</v>
+        <v>271603</v>
       </c>
       <c r="F280" s="8" t="inlineStr">
         <is>
-          <t>INV-2026-27/0308</t>
+          <t>INV-2026-27/0307</t>
         </is>
       </c>
       <c r="G280" s="8" t="inlineStr"/>
@@ -12659,46 +12651,42 @@
       <c r="J280" s="10" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B281" s="5" t="inlineStr">
+      <c r="A281" s="8" t="inlineStr">
+        <is>
+          <t>Only in Zoho - import</t>
+        </is>
+      </c>
+      <c r="B281" s="8" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0846</t>
         </is>
       </c>
-      <c r="C281" s="5" t="inlineStr">
+      <c r="C281" s="8" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="D281" s="5" t="inlineStr">
-        <is>
-          <t>Kamakhya Traders</t>
-        </is>
-      </c>
-      <c r="E281" s="6" t="n">
+      <c r="D281" s="8" t="inlineStr">
+        <is>
+          <t>NB Traders</t>
+        </is>
+      </c>
+      <c r="E281" s="9" t="n">
         <v>275100</v>
       </c>
-      <c r="F281" s="5" t="inlineStr">
-        <is>
-          <t>INV-2026-27/0309</t>
-        </is>
-      </c>
-      <c r="G281" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0829</t>
-        </is>
-      </c>
-      <c r="H281" s="5" t="inlineStr"/>
-      <c r="I281" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J281" s="7" t="inlineStr"/>
+      <c r="F281" s="8" t="inlineStr">
+        <is>
+          <t>INV-2026-27/0308</t>
+        </is>
+      </c>
+      <c r="G281" s="8" t="inlineStr"/>
+      <c r="H281" s="8" t="inlineStr"/>
+      <c r="I281" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J281" s="10" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
@@ -12718,20 +12706,20 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>PD Egg Store</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E282" s="6" t="n">
-        <v>266920</v>
+        <v>275100</v>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>INV-2026-27/0310</t>
+          <t>INV-2026-27/0309</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0828</t>
+          <t>A-INV-EG-27-0829</t>
         </is>
       </c>
       <c r="H282" s="5" t="inlineStr"/>
@@ -12743,80 +12731,84 @@
       <c r="J282" s="7" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="8" t="inlineStr">
+      <c r="A283" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B283" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0848</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>PD Egg Store</t>
+        </is>
+      </c>
+      <c r="E283" s="6" t="n">
+        <v>266920</v>
+      </c>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>INV-2026-27/0310</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0828</t>
+        </is>
+      </c>
+      <c r="H283" s="5" t="inlineStr"/>
+      <c r="I283" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J283" s="7" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="8" t="inlineStr">
         <is>
           <t>Only in Zoho - import</t>
         </is>
       </c>
-      <c r="B283" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0848</t>
-        </is>
-      </c>
-      <c r="C283" s="8" t="inlineStr">
+      <c r="B284" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0849</t>
+        </is>
+      </c>
+      <c r="C284" s="8" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="D283" s="8" t="inlineStr">
+      <c r="D284" s="8" t="inlineStr">
         <is>
           <t>NB Traders</t>
         </is>
       </c>
-      <c r="E283" s="9" t="n">
+      <c r="E284" s="9" t="n">
         <v>275100</v>
       </c>
-      <c r="F283" s="8" t="inlineStr">
+      <c r="F284" s="8" t="inlineStr">
         <is>
           <t>INV-2026-27/0311</t>
         </is>
       </c>
-      <c r="G283" s="8" t="inlineStr"/>
-      <c r="H283" s="8" t="inlineStr"/>
-      <c r="I283" s="8" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J283" s="10" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="11" t="inlineStr">
-        <is>
-          <t>Only in niko - keep</t>
-        </is>
-      </c>
-      <c r="B284" s="11" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0849</t>
-        </is>
-      </c>
-      <c r="C284" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="D284" s="11" t="inlineStr">
-        <is>
-          <t>NB Traders</t>
-        </is>
-      </c>
-      <c r="E284" s="12" t="n">
-        <v>550200</v>
-      </c>
-      <c r="F284" s="11" t="inlineStr"/>
-      <c r="G284" s="11" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0827</t>
-        </is>
-      </c>
-      <c r="H284" s="11" t="inlineStr"/>
-      <c r="I284" s="11" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J284" s="13" t="inlineStr"/>
+      <c r="G284" s="8" t="inlineStr"/>
+      <c r="H284" s="8" t="inlineStr"/>
+      <c r="I284" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J284" s="10" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
@@ -12836,16 +12828,16 @@
       </c>
       <c r="D285" s="11" t="inlineStr">
         <is>
-          <t>HKD Egg Traders</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E285" s="12" t="n">
-        <v>278695</v>
+        <v>550200</v>
       </c>
       <c r="F285" s="11" t="inlineStr"/>
       <c r="G285" s="11" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0831</t>
+          <t>A-INV-EG-27-0827</t>
         </is>
       </c>
       <c r="H285" s="11" t="inlineStr"/>
@@ -12857,46 +12849,42 @@
       <c r="J285" s="13" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B286" s="5" t="inlineStr">
+      <c r="A286" s="11" t="inlineStr">
+        <is>
+          <t>Only in niko - keep</t>
+        </is>
+      </c>
+      <c r="B286" s="11" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0851</t>
         </is>
       </c>
-      <c r="C286" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="D286" s="5" t="inlineStr">
-        <is>
-          <t>Josef Ali</t>
-        </is>
-      </c>
-      <c r="E286" s="6" t="n">
-        <v>162545</v>
-      </c>
-      <c r="F286" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0836</t>
-        </is>
-      </c>
-      <c r="G286" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0832</t>
-        </is>
-      </c>
-      <c r="H286" s="5" t="inlineStr"/>
-      <c r="I286" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J286" s="7" t="inlineStr"/>
+      <c r="C286" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D286" s="11" t="inlineStr">
+        <is>
+          <t>HKD Egg Traders</t>
+        </is>
+      </c>
+      <c r="E286" s="12" t="n">
+        <v>278695</v>
+      </c>
+      <c r="F286" s="11" t="inlineStr"/>
+      <c r="G286" s="11" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0831</t>
+        </is>
+      </c>
+      <c r="H286" s="11" t="inlineStr"/>
+      <c r="I286" s="11" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J286" s="13" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
@@ -12916,20 +12904,20 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Josef Ali</t>
         </is>
       </c>
       <c r="E287" s="6" t="n">
-        <v>539600</v>
+        <v>162545</v>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0837</t>
+          <t>A-INV-EG-27-0836</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0833</t>
+          <t>A-INV-EG-27-0832</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr"/>
@@ -12958,20 +12946,20 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Surjya Store</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E288" s="6" t="n">
-        <v>275100</v>
+        <v>539600</v>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0838</t>
+          <t>A-INV-EG-27-0837</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0834</t>
+          <t>A-INV-EG-27-0833</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr"/>
@@ -13000,7 +12988,7 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>Surjya Store</t>
         </is>
       </c>
       <c r="E289" s="6" t="n">
@@ -13008,12 +12996,12 @@
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0839</t>
+          <t>A-INV-EG-27-0838</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0835</t>
+          <t>A-INV-EG-27-0834</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr"/>
@@ -13042,20 +13030,20 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Chowdhury n Sons</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E290" s="6" t="n">
-        <v>286780</v>
+        <v>275100</v>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0840</t>
+          <t>A-INV-EG-27-0839</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0804</t>
+          <t>A-INV-EG-27-0835</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr"/>
@@ -13067,42 +13055,46 @@
       <c r="J290" s="7" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="8" t="inlineStr">
-        <is>
-          <t>Only in Zoho - import</t>
-        </is>
-      </c>
-      <c r="B291" s="8" t="inlineStr">
+      <c r="A291" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0856</t>
         </is>
       </c>
-      <c r="C291" s="8" t="inlineStr">
+      <c r="C291" s="5" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="D291" s="8" t="inlineStr">
-        <is>
-          <t>PD Egg Store</t>
-        </is>
-      </c>
-      <c r="E291" s="9" t="n">
-        <v>296250</v>
-      </c>
-      <c r="F291" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0841</t>
-        </is>
-      </c>
-      <c r="G291" s="8" t="inlineStr"/>
-      <c r="H291" s="8" t="inlineStr"/>
-      <c r="I291" s="8" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="J291" s="10" t="inlineStr"/>
+      <c r="D291" s="5" t="inlineStr">
+        <is>
+          <t>Chowdhury n Sons</t>
+        </is>
+      </c>
+      <c r="E291" s="6" t="n">
+        <v>286780</v>
+      </c>
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0840</t>
+        </is>
+      </c>
+      <c r="G291" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0804</t>
+        </is>
+      </c>
+      <c r="H291" s="5" t="inlineStr"/>
+      <c r="I291" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J291" s="7" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="8" t="inlineStr">
@@ -13122,15 +13114,15 @@
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>Protein Shop</t>
+          <t>PD Egg Store</t>
         </is>
       </c>
       <c r="E292" s="9" t="n">
-        <v>148125</v>
+        <v>296250</v>
       </c>
       <c r="F292" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0842</t>
+          <t>A-INV-EG-27-0841</t>
         </is>
       </c>
       <c r="G292" s="8" t="inlineStr"/>
@@ -13160,22 +13152,22 @@
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Protein Shop</t>
         </is>
       </c>
       <c r="E293" s="9" t="n">
-        <v>262550</v>
+        <v>148125</v>
       </c>
       <c r="F293" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0843</t>
+          <t>A-INV-EG-27-0842</t>
         </is>
       </c>
       <c r="G293" s="8" t="inlineStr"/>
       <c r="H293" s="8" t="inlineStr"/>
       <c r="I293" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J293" s="10" t="inlineStr"/>
@@ -13193,27 +13185,27 @@
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>Sahil Egg Center</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E294" s="9" t="n">
-        <v>1072266</v>
+        <v>262550</v>
       </c>
       <c r="F294" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0844</t>
+          <t>A-INV-EG-27-0843</t>
         </is>
       </c>
       <c r="G294" s="8" t="inlineStr"/>
       <c r="H294" s="8" t="inlineStr"/>
       <c r="I294" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J294" s="10" t="inlineStr"/>
@@ -13236,22 +13228,22 @@
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>Sahil Egg Center</t>
         </is>
       </c>
       <c r="E295" s="9" t="n">
-        <v>275100</v>
+        <v>1072266</v>
       </c>
       <c r="F295" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0845</t>
+          <t>A-INV-EG-27-0844</t>
         </is>
       </c>
       <c r="G295" s="8" t="inlineStr"/>
       <c r="H295" s="8" t="inlineStr"/>
       <c r="I295" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J295" s="10" t="inlineStr"/>
@@ -13274,15 +13266,15 @@
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>M/s Mayengbam Enterprises</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E296" s="9" t="n">
-        <v>1185340</v>
+        <v>275100</v>
       </c>
       <c r="F296" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0846</t>
+          <t>A-INV-EG-27-0845</t>
         </is>
       </c>
       <c r="G296" s="8" t="inlineStr"/>
@@ -13295,84 +13287,84 @@
       <c r="J296" s="10" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B297" s="5" t="inlineStr">
+      <c r="A297" s="8" t="inlineStr">
+        <is>
+          <t>Only in Zoho - import</t>
+        </is>
+      </c>
+      <c r="B297" s="8" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0862</t>
         </is>
       </c>
-      <c r="C297" s="5" t="inlineStr">
+      <c r="C297" s="8" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="D297" s="8" t="inlineStr">
+        <is>
+          <t>M/s Mayengbam Enterprises</t>
+        </is>
+      </c>
+      <c r="E297" s="9" t="n">
+        <v>1185340</v>
+      </c>
+      <c r="F297" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0846</t>
+        </is>
+      </c>
+      <c r="G297" s="8" t="inlineStr"/>
+      <c r="H297" s="8" t="inlineStr"/>
+      <c r="I297" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J297" s="10" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0863</t>
+        </is>
+      </c>
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
         <is>
           <t>Kamakhya Traders</t>
         </is>
       </c>
-      <c r="E297" s="6" t="n">
+      <c r="E298" s="6" t="n">
         <v>275100</v>
       </c>
-      <c r="F297" s="5" t="inlineStr">
+      <c r="F298" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0847</t>
         </is>
       </c>
-      <c r="G297" s="5" t="inlineStr">
+      <c r="G298" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0805</t>
         </is>
       </c>
-      <c r="H297" s="5" t="inlineStr"/>
-      <c r="I297" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J297" s="7" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="8" t="inlineStr">
-        <is>
-          <t>Only in Zoho - import</t>
-        </is>
-      </c>
-      <c r="B298" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0863</t>
-        </is>
-      </c>
-      <c r="C298" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="D298" s="8" t="inlineStr">
-        <is>
-          <t>DN Store</t>
-        </is>
-      </c>
-      <c r="E298" s="9" t="n">
-        <v>283825</v>
-      </c>
-      <c r="F298" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0848</t>
-        </is>
-      </c>
-      <c r="G298" s="8" t="inlineStr"/>
-      <c r="H298" s="8" t="inlineStr"/>
-      <c r="I298" s="8" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J298" s="10" t="inlineStr"/>
+      <c r="H298" s="5" t="inlineStr"/>
+      <c r="I298" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J298" s="7" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="8" t="inlineStr">
@@ -13392,15 +13384,15 @@
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>M/s Annapurna Bakery</t>
+          <t>DN Store</t>
         </is>
       </c>
       <c r="E299" s="9" t="n">
-        <v>119670</v>
+        <v>283825</v>
       </c>
       <c r="F299" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0849</t>
+          <t>A-INV-EG-27-0848</t>
         </is>
       </c>
       <c r="G299" s="8" t="inlineStr"/>
@@ -13430,15 +13422,15 @@
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>Rahman Store</t>
+          <t>M/s Annapurna Bakery</t>
         </is>
       </c>
       <c r="E300" s="9" t="n">
-        <v>1159105</v>
+        <v>119670</v>
       </c>
       <c r="F300" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0850</t>
+          <t>A-INV-EG-27-0849</t>
         </is>
       </c>
       <c r="G300" s="8" t="inlineStr"/>
@@ -13463,20 +13455,20 @@
       </c>
       <c r="C301" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Rahman Store</t>
         </is>
       </c>
       <c r="E301" s="9" t="n">
-        <v>529200</v>
+        <v>1159105</v>
       </c>
       <c r="F301" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0851</t>
+          <t>A-INV-EG-27-0850</t>
         </is>
       </c>
       <c r="G301" s="8" t="inlineStr"/>
@@ -13506,22 +13498,22 @@
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E302" s="9" t="n">
-        <v>463050</v>
+        <v>529200</v>
       </c>
       <c r="F302" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0852</t>
+          <t>A-INV-EG-27-0851</t>
         </is>
       </c>
       <c r="G302" s="8" t="inlineStr"/>
       <c r="H302" s="8" t="inlineStr"/>
       <c r="I302" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J302" s="10" t="inlineStr"/>
@@ -13544,22 +13536,22 @@
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E303" s="9" t="n">
-        <v>529200</v>
+        <v>463050</v>
       </c>
       <c r="F303" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0853</t>
+          <t>A-INV-EG-27-0852</t>
         </is>
       </c>
       <c r="G303" s="8" t="inlineStr"/>
       <c r="H303" s="8" t="inlineStr"/>
       <c r="I303" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J303" s="10" t="inlineStr"/>
@@ -13582,15 +13574,15 @@
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>DG Egg Point (Debajeet Gogoi)</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E304" s="9" t="n">
-        <v>212500</v>
+        <v>529200</v>
       </c>
       <c r="F304" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0854</t>
+          <t>A-INV-EG-27-0853</t>
         </is>
       </c>
       <c r="G304" s="8" t="inlineStr"/>
@@ -13620,22 +13612,22 @@
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>Protein Shop</t>
+          <t>DG Egg Point (Debajeet Gogoi)</t>
         </is>
       </c>
       <c r="E305" s="9" t="n">
-        <v>142300</v>
+        <v>212500</v>
       </c>
       <c r="F305" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0855</t>
+          <t>A-INV-EG-27-0854</t>
         </is>
       </c>
       <c r="G305" s="8" t="inlineStr"/>
       <c r="H305" s="8" t="inlineStr"/>
       <c r="I305" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J305" s="10" t="inlineStr"/>
@@ -13658,22 +13650,22 @@
       </c>
       <c r="D306" s="8" t="inlineStr">
         <is>
-          <t>Sayedur Rahman</t>
+          <t>Protein Shop</t>
         </is>
       </c>
       <c r="E306" s="9" t="n">
-        <v>266940</v>
+        <v>142300</v>
       </c>
       <c r="F306" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0856</t>
+          <t>A-INV-EG-27-0855</t>
         </is>
       </c>
       <c r="G306" s="8" t="inlineStr"/>
       <c r="H306" s="8" t="inlineStr"/>
       <c r="I306" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J306" s="10" t="inlineStr"/>
@@ -13696,15 +13688,15 @@
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>DD Egg Point (Gahin Handique)</t>
+          <t>Sayedur Rahman</t>
         </is>
       </c>
       <c r="E307" s="9" t="n">
-        <v>287500</v>
+        <v>266940</v>
       </c>
       <c r="F307" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0857</t>
+          <t>A-INV-EG-27-0856</t>
         </is>
       </c>
       <c r="G307" s="8" t="inlineStr"/>
@@ -13729,20 +13721,20 @@
       </c>
       <c r="C308" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D308" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>DD Egg Point (Gahin Handique)</t>
         </is>
       </c>
       <c r="E308" s="9" t="n">
-        <v>198450</v>
+        <v>287500</v>
       </c>
       <c r="F308" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0858</t>
+          <t>A-INV-EG-27-0857</t>
         </is>
       </c>
       <c r="G308" s="8" t="inlineStr"/>
@@ -13772,15 +13764,15 @@
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E309" s="9" t="n">
-        <v>264600</v>
+        <v>198450</v>
       </c>
       <c r="F309" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0859</t>
+          <t>A-INV-EG-27-0858</t>
         </is>
       </c>
       <c r="G309" s="8" t="inlineStr"/>
@@ -13810,15 +13802,15 @@
       </c>
       <c r="D310" s="8" t="inlineStr">
         <is>
-          <t>Chowdhury n Sons</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E310" s="9" t="n">
-        <v>1091700</v>
+        <v>264600</v>
       </c>
       <c r="F310" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0860</t>
+          <t>A-INV-EG-27-0859</t>
         </is>
       </c>
       <c r="G310" s="8" t="inlineStr"/>
@@ -13848,15 +13840,15 @@
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>Josef Ali</t>
+          <t>Chowdhury n Sons</t>
         </is>
       </c>
       <c r="E311" s="9" t="n">
-        <v>171195</v>
+        <v>1091700</v>
       </c>
       <c r="F311" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0861</t>
+          <t>A-INV-EG-27-0860</t>
         </is>
       </c>
       <c r="G311" s="8" t="inlineStr"/>
@@ -13886,15 +13878,15 @@
       </c>
       <c r="D312" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Josef Ali</t>
         </is>
       </c>
       <c r="E312" s="9" t="n">
-        <v>264600</v>
+        <v>171195</v>
       </c>
       <c r="F312" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0862</t>
+          <t>A-INV-EG-27-0861</t>
         </is>
       </c>
       <c r="G312" s="8" t="inlineStr"/>
@@ -13924,101 +13916,101 @@
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>Zakir Egg Store</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E313" s="9" t="n">
-        <v>1226922</v>
+        <v>264600</v>
       </c>
       <c r="F313" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0863</t>
+          <t>A-INV-EG-27-0862</t>
         </is>
       </c>
       <c r="G313" s="8" t="inlineStr"/>
       <c r="H313" s="8" t="inlineStr"/>
       <c r="I313" s="8" t="inlineStr">
         <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J313" s="10" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="8" t="inlineStr">
+        <is>
+          <t>Only in Zoho - import</t>
+        </is>
+      </c>
+      <c r="B314" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0879</t>
+        </is>
+      </c>
+      <c r="C314" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D314" s="8" t="inlineStr">
+        <is>
+          <t>Zakir Egg Store</t>
+        </is>
+      </c>
+      <c r="E314" s="9" t="n">
+        <v>1226922</v>
+      </c>
+      <c r="F314" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0863</t>
+        </is>
+      </c>
+      <c r="G314" s="8" t="inlineStr"/>
+      <c r="H314" s="8" t="inlineStr"/>
+      <c r="I314" s="8" t="inlineStr">
+        <is>
           <t>overdue</t>
         </is>
       </c>
-      <c r="J313" s="10" t="inlineStr"/>
-    </row>
-    <row r="314">
-      <c r="A314" s="11" t="inlineStr">
+      <c r="J314" s="10" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="11" t="inlineStr">
         <is>
           <t>Only in niko - keep</t>
         </is>
       </c>
-      <c r="B314" s="11" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0879</t>
-        </is>
-      </c>
-      <c r="C314" s="11" t="inlineStr">
+      <c r="B315" s="11" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0880</t>
+        </is>
+      </c>
+      <c r="C315" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D314" s="11" t="inlineStr">
+      <c r="D315" s="11" t="inlineStr">
         <is>
           <t>Sahil Egg Center</t>
         </is>
       </c>
-      <c r="E314" s="12" t="n">
+      <c r="E315" s="12" t="n">
         <v>1165466</v>
       </c>
-      <c r="F314" s="11" t="inlineStr"/>
-      <c r="G314" s="11" t="inlineStr">
+      <c r="F315" s="11" t="inlineStr"/>
+      <c r="G315" s="11" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0836</t>
         </is>
       </c>
-      <c r="H314" s="11" t="inlineStr"/>
-      <c r="I314" s="11" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J314" s="13" t="inlineStr"/>
-    </row>
-    <row r="315">
-      <c r="A315" s="8" t="inlineStr">
-        <is>
-          <t>Only in Zoho - import</t>
-        </is>
-      </c>
-      <c r="B315" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0880</t>
-        </is>
-      </c>
-      <c r="C315" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="D315" s="8" t="inlineStr">
-        <is>
-          <t>Kamakhya Traders</t>
-        </is>
-      </c>
-      <c r="E315" s="9" t="n">
-        <v>258300</v>
-      </c>
-      <c r="F315" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0864</t>
-        </is>
-      </c>
-      <c r="G315" s="8" t="inlineStr"/>
-      <c r="H315" s="8" t="inlineStr"/>
-      <c r="I315" s="8" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J315" s="10" t="inlineStr"/>
+      <c r="H315" s="11" t="inlineStr"/>
+      <c r="I315" s="11" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J315" s="13" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="8" t="inlineStr">
@@ -14038,15 +14030,15 @@
       </c>
       <c r="D316" s="8" t="inlineStr">
         <is>
-          <t>Fariha Store</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E316" s="9" t="n">
-        <v>203460</v>
+        <v>258300</v>
       </c>
       <c r="F316" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0865</t>
+          <t>A-INV-EG-27-0864</t>
         </is>
       </c>
       <c r="G316" s="8" t="inlineStr"/>
@@ -14076,15 +14068,15 @@
       </c>
       <c r="D317" s="8" t="inlineStr">
         <is>
-          <t>Ali Whiz</t>
+          <t>Fariha Store</t>
         </is>
       </c>
       <c r="E317" s="9" t="n">
-        <v>1128503</v>
+        <v>203460</v>
       </c>
       <c r="F317" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0866</t>
+          <t>A-INV-EG-27-0865</t>
         </is>
       </c>
       <c r="G317" s="8" t="inlineStr"/>
@@ -14114,22 +14106,22 @@
       </c>
       <c r="D318" s="8" t="inlineStr">
         <is>
-          <t>Surjya Store</t>
+          <t>Ali Whiz</t>
         </is>
       </c>
       <c r="E318" s="9" t="n">
-        <v>253000</v>
+        <v>1128503</v>
       </c>
       <c r="F318" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0867</t>
+          <t>A-INV-EG-27-0866</t>
         </is>
       </c>
       <c r="G318" s="8" t="inlineStr"/>
       <c r="H318" s="8" t="inlineStr"/>
       <c r="I318" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J318" s="10" t="inlineStr"/>
@@ -14152,22 +14144,22 @@
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>Surjya Store</t>
         </is>
       </c>
       <c r="E319" s="9" t="n">
-        <v>253050</v>
+        <v>253000</v>
       </c>
       <c r="F319" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0868</t>
+          <t>A-INV-EG-27-0867</t>
         </is>
       </c>
       <c r="G319" s="8" t="inlineStr"/>
       <c r="H319" s="8" t="inlineStr"/>
       <c r="I319" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J319" s="10" t="inlineStr"/>
@@ -14190,22 +14182,22 @@
       </c>
       <c r="D320" s="8" t="inlineStr">
         <is>
-          <t>PD Egg Store</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E320" s="9" t="n">
-        <v>258300</v>
+        <v>253050</v>
       </c>
       <c r="F320" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0869</t>
+          <t>A-INV-EG-27-0868</t>
         </is>
       </c>
       <c r="G320" s="8" t="inlineStr"/>
       <c r="H320" s="8" t="inlineStr"/>
       <c r="I320" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J320" s="10" t="inlineStr"/>
@@ -14228,7 +14220,7 @@
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>PD Egg Store</t>
         </is>
       </c>
       <c r="E321" s="9" t="n">
@@ -14236,14 +14228,14 @@
       </c>
       <c r="F321" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0870</t>
+          <t>A-INV-EG-27-0869</t>
         </is>
       </c>
       <c r="G321" s="8" t="inlineStr"/>
       <c r="H321" s="8" t="inlineStr"/>
       <c r="I321" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J321" s="10" t="inlineStr"/>
@@ -14266,7 +14258,7 @@
       </c>
       <c r="D322" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E322" s="9" t="n">
@@ -14274,7 +14266,7 @@
       </c>
       <c r="F322" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0871</t>
+          <t>A-INV-EG-27-0870</t>
         </is>
       </c>
       <c r="G322" s="8" t="inlineStr"/>
@@ -14304,15 +14296,15 @@
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>Ashim Dey</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E323" s="9" t="n">
-        <v>148680</v>
+        <v>258300</v>
       </c>
       <c r="F323" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0872</t>
+          <t>A-INV-EG-27-0871</t>
         </is>
       </c>
       <c r="G323" s="8" t="inlineStr"/>
@@ -14337,20 +14329,20 @@
       </c>
       <c r="C324" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D324" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>Ashim Dey</t>
         </is>
       </c>
       <c r="E324" s="9" t="n">
-        <v>260400</v>
+        <v>148680</v>
       </c>
       <c r="F324" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0873</t>
+          <t>A-INV-EG-27-0872</t>
         </is>
       </c>
       <c r="G324" s="8" t="inlineStr"/>
@@ -14380,15 +14372,15 @@
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E325" s="9" t="n">
-        <v>385300</v>
+        <v>260400</v>
       </c>
       <c r="F325" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0874</t>
+          <t>A-INV-EG-27-0873</t>
         </is>
       </c>
       <c r="G325" s="8" t="inlineStr"/>
@@ -14418,22 +14410,22 @@
       </c>
       <c r="D326" s="8" t="inlineStr">
         <is>
-          <t>Protein Shop</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E326" s="9" t="n">
-        <v>143220</v>
+        <v>385300</v>
       </c>
       <c r="F326" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0875</t>
+          <t>A-INV-EG-27-0874</t>
         </is>
       </c>
       <c r="G326" s="8" t="inlineStr"/>
       <c r="H326" s="8" t="inlineStr"/>
       <c r="I326" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J326" s="10" t="inlineStr"/>
@@ -14456,22 +14448,22 @@
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>Fresh Egg Traders</t>
+          <t>Protein Shop</t>
         </is>
       </c>
       <c r="E327" s="9" t="n">
-        <v>1164114</v>
+        <v>143220</v>
       </c>
       <c r="F327" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0876</t>
+          <t>A-INV-EG-27-0875</t>
         </is>
       </c>
       <c r="G327" s="8" t="inlineStr"/>
       <c r="H327" s="8" t="inlineStr"/>
       <c r="I327" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J327" s="10" t="inlineStr"/>
@@ -14494,15 +14486,15 @@
       </c>
       <c r="D328" s="8" t="inlineStr">
         <is>
-          <t>DG Egg Point (Debajeet Gogoi)</t>
+          <t>Fresh Egg Traders</t>
         </is>
       </c>
       <c r="E328" s="9" t="n">
-        <v>212330</v>
+        <v>1164114</v>
       </c>
       <c r="F328" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0877</t>
+          <t>A-INV-EG-27-0876</t>
         </is>
       </c>
       <c r="G328" s="8" t="inlineStr"/>
@@ -14532,15 +14524,15 @@
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>DG Egg Point (Debajeet Gogoi)</t>
         </is>
       </c>
       <c r="E329" s="9" t="n">
-        <v>249800</v>
+        <v>212330</v>
       </c>
       <c r="F329" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0878</t>
+          <t>A-INV-EG-27-0877</t>
         </is>
       </c>
       <c r="G329" s="8" t="inlineStr"/>
@@ -14570,15 +14562,15 @@
       </c>
       <c r="D330" s="8" t="inlineStr">
         <is>
-          <t>M/s Mayengbam Enterprises</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E330" s="9" t="n">
-        <v>1175769</v>
+        <v>249800</v>
       </c>
       <c r="F330" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0879</t>
+          <t>A-INV-EG-27-0878</t>
         </is>
       </c>
       <c r="G330" s="8" t="inlineStr"/>
@@ -14608,15 +14600,15 @@
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>M/s Annapurna Bakery</t>
+          <t>M/s Mayengbam Enterprises</t>
         </is>
       </c>
       <c r="E331" s="9" t="n">
-        <v>156510</v>
+        <v>1175769</v>
       </c>
       <c r="F331" s="8" t="inlineStr">
         <is>
-          <t>INV-2026-27/0313</t>
+          <t>A-INV-EG-27-0879</t>
         </is>
       </c>
       <c r="G331" s="8" t="inlineStr"/>
@@ -14641,20 +14633,20 @@
       </c>
       <c r="C332" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D332" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>M/s Annapurna Bakery</t>
         </is>
       </c>
       <c r="E332" s="9" t="n">
-        <v>264600</v>
+        <v>156510</v>
       </c>
       <c r="F332" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0880</t>
+          <t>INV-2026-27/0313</t>
         </is>
       </c>
       <c r="G332" s="8" t="inlineStr"/>
@@ -14684,7 +14676,7 @@
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E333" s="9" t="n">
@@ -14692,7 +14684,7 @@
       </c>
       <c r="F333" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0881</t>
+          <t>A-INV-EG-27-0880</t>
         </is>
       </c>
       <c r="G333" s="8" t="inlineStr"/>
@@ -14722,15 +14714,15 @@
       </c>
       <c r="D334" s="8" t="inlineStr">
         <is>
-          <t>DN Store</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E334" s="9" t="n">
-        <v>259300</v>
+        <v>264600</v>
       </c>
       <c r="F334" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0882</t>
+          <t>A-INV-EG-27-0881</t>
         </is>
       </c>
       <c r="G334" s="8" t="inlineStr"/>
@@ -14760,15 +14752,15 @@
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>DD Egg Point (Gahin Handique)</t>
+          <t>DN Store</t>
         </is>
       </c>
       <c r="E335" s="9" t="n">
-        <v>291050</v>
+        <v>259300</v>
       </c>
       <c r="F335" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0883</t>
+          <t>A-INV-EG-27-0882</t>
         </is>
       </c>
       <c r="G335" s="8" t="inlineStr"/>
@@ -14798,15 +14790,15 @@
       </c>
       <c r="D336" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>DD Egg Point (Gahin Handique)</t>
         </is>
       </c>
       <c r="E336" s="9" t="n">
-        <v>264600</v>
+        <v>291050</v>
       </c>
       <c r="F336" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0884</t>
+          <t>A-INV-EG-27-0883</t>
         </is>
       </c>
       <c r="G336" s="8" t="inlineStr"/>
@@ -14836,15 +14828,15 @@
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Rahman Store</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E337" s="9" t="n">
-        <v>1132450</v>
+        <v>264600</v>
       </c>
       <c r="F337" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0885</t>
+          <t>A-INV-EG-27-0884</t>
         </is>
       </c>
       <c r="G337" s="8" t="inlineStr"/>
@@ -14874,15 +14866,15 @@
       </c>
       <c r="D338" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Rahman Store</t>
         </is>
       </c>
       <c r="E338" s="9" t="n">
-        <v>264600</v>
+        <v>1132450</v>
       </c>
       <c r="F338" s="8" t="inlineStr">
         <is>
-          <t>INV-2026-27/0314</t>
+          <t>A-INV-EG-27-0885</t>
         </is>
       </c>
       <c r="G338" s="8" t="inlineStr"/>
@@ -14907,20 +14899,20 @@
       </c>
       <c r="C339" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E339" s="9" t="n">
-        <v>266700</v>
+        <v>264600</v>
       </c>
       <c r="F339" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0886</t>
+          <t>INV-2026-27/0314</t>
         </is>
       </c>
       <c r="G339" s="8" t="inlineStr"/>
@@ -14950,15 +14942,15 @@
       </c>
       <c r="D340" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E340" s="9" t="n">
-        <v>789500</v>
+        <v>266700</v>
       </c>
       <c r="F340" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0887</t>
+          <t>A-INV-EG-27-0886</t>
         </is>
       </c>
       <c r="G340" s="8" t="inlineStr"/>
@@ -14988,15 +14980,15 @@
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>Josef Ali</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E341" s="9" t="n">
-        <v>173355</v>
+        <v>789500</v>
       </c>
       <c r="F341" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0888</t>
+          <t>A-INV-EG-27-0887</t>
         </is>
       </c>
       <c r="G341" s="8" t="inlineStr"/>
@@ -15026,22 +15018,22 @@
       </c>
       <c r="D342" s="8" t="inlineStr">
         <is>
-          <t>Protein Shop</t>
+          <t>Josef Ali</t>
         </is>
       </c>
       <c r="E342" s="9" t="n">
-        <v>146685</v>
+        <v>173355</v>
       </c>
       <c r="F342" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0889</t>
+          <t>A-INV-EG-27-0888</t>
         </is>
       </c>
       <c r="G342" s="8" t="inlineStr"/>
       <c r="H342" s="8" t="inlineStr"/>
       <c r="I342" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J342" s="10" t="inlineStr"/>
@@ -15064,22 +15056,22 @@
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Protein Shop</t>
         </is>
       </c>
       <c r="E343" s="9" t="n">
-        <v>522800</v>
+        <v>146685</v>
       </c>
       <c r="F343" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0890</t>
+          <t>A-INV-EG-27-0889</t>
         </is>
       </c>
       <c r="G343" s="8" t="inlineStr"/>
       <c r="H343" s="8" t="inlineStr"/>
       <c r="I343" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J343" s="10" t="inlineStr"/>
@@ -15097,20 +15089,20 @@
       </c>
       <c r="C344" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D344" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E344" s="9" t="n">
-        <v>268800</v>
+        <v>522800</v>
       </c>
       <c r="F344" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0891</t>
+          <t>A-INV-EG-27-0890</t>
         </is>
       </c>
       <c r="G344" s="8" t="inlineStr"/>
@@ -15140,7 +15132,7 @@
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E345" s="9" t="n">
@@ -15148,7 +15140,7 @@
       </c>
       <c r="F345" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0892</t>
+          <t>A-INV-EG-27-0891</t>
         </is>
       </c>
       <c r="G345" s="8" t="inlineStr"/>
@@ -15178,7 +15170,7 @@
       </c>
       <c r="D346" s="8" t="inlineStr">
         <is>
-          <t>Sayedur Rahman</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E346" s="9" t="n">
@@ -15186,7 +15178,7 @@
       </c>
       <c r="F346" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0893</t>
+          <t>A-INV-EG-27-0892</t>
         </is>
       </c>
       <c r="G346" s="8" t="inlineStr"/>
@@ -15216,7 +15208,7 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>Surjya Store</t>
+          <t>Sayedur Rahman</t>
         </is>
       </c>
       <c r="E347" s="9" t="n">
@@ -15224,14 +15216,14 @@
       </c>
       <c r="F347" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0894</t>
+          <t>A-INV-EG-27-0893</t>
         </is>
       </c>
       <c r="G347" s="8" t="inlineStr"/>
       <c r="H347" s="8" t="inlineStr"/>
       <c r="I347" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J347" s="10" t="inlineStr"/>
@@ -15254,22 +15246,22 @@
       </c>
       <c r="D348" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Surjya Store</t>
         </is>
       </c>
       <c r="E348" s="9" t="n">
-        <v>532300</v>
+        <v>268800</v>
       </c>
       <c r="F348" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0895</t>
+          <t>A-INV-EG-27-0894</t>
         </is>
       </c>
       <c r="G348" s="8" t="inlineStr"/>
       <c r="H348" s="8" t="inlineStr"/>
       <c r="I348" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J348" s="10" t="inlineStr"/>
@@ -15292,15 +15284,15 @@
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>Ashim Dey</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E349" s="9" t="n">
-        <v>154920</v>
+        <v>532300</v>
       </c>
       <c r="F349" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0896</t>
+          <t>A-INV-EG-27-0895</t>
         </is>
       </c>
       <c r="G349" s="8" t="inlineStr"/>
@@ -15325,20 +15317,20 @@
       </c>
       <c r="C350" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D350" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Ashim Dey</t>
         </is>
       </c>
       <c r="E350" s="9" t="n">
-        <v>537600</v>
+        <v>154920</v>
       </c>
       <c r="F350" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0897</t>
+          <t>A-INV-EG-27-0896</t>
         </is>
       </c>
       <c r="G350" s="8" t="inlineStr"/>
@@ -15368,15 +15360,15 @@
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E351" s="9" t="n">
-        <v>336000</v>
+        <v>537600</v>
       </c>
       <c r="F351" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0898</t>
+          <t>A-INV-EG-27-0897</t>
         </is>
       </c>
       <c r="G351" s="8" t="inlineStr"/>
@@ -15406,15 +15398,15 @@
       </c>
       <c r="D352" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E352" s="9" t="n">
-        <v>161280</v>
+        <v>336000</v>
       </c>
       <c r="F352" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0899</t>
+          <t>A-INV-EG-27-0898</t>
         </is>
       </c>
       <c r="G352" s="8" t="inlineStr"/>
@@ -15444,15 +15436,15 @@
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E353" s="9" t="n">
-        <v>268800</v>
+        <v>161280</v>
       </c>
       <c r="F353" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0900</t>
+          <t>A-INV-EG-27-0899</t>
         </is>
       </c>
       <c r="G353" s="8" t="inlineStr"/>
@@ -15482,7 +15474,7 @@
       </c>
       <c r="D354" s="8" t="inlineStr">
         <is>
-          <t>DN Store</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E354" s="9" t="n">
@@ -15490,7 +15482,7 @@
       </c>
       <c r="F354" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0901</t>
+          <t>A-INV-EG-27-0900</t>
         </is>
       </c>
       <c r="G354" s="8" t="inlineStr"/>
@@ -15520,15 +15512,15 @@
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>DG Egg Point (Debajeet Gogoi)</t>
+          <t>DN Store</t>
         </is>
       </c>
       <c r="E355" s="9" t="n">
-        <v>219470</v>
+        <v>268800</v>
       </c>
       <c r="F355" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0902</t>
+          <t>A-INV-EG-27-0901</t>
         </is>
       </c>
       <c r="G355" s="8" t="inlineStr"/>
@@ -15558,22 +15550,22 @@
       </c>
       <c r="D356" s="8" t="inlineStr">
         <is>
-          <t>Protein Shop</t>
+          <t>DG Egg Point (Debajeet Gogoi)</t>
         </is>
       </c>
       <c r="E356" s="9" t="n">
-        <v>147840</v>
+        <v>219470</v>
       </c>
       <c r="F356" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0903</t>
+          <t>A-INV-EG-27-0902</t>
         </is>
       </c>
       <c r="G356" s="8" t="inlineStr"/>
       <c r="H356" s="8" t="inlineStr"/>
       <c r="I356" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J356" s="10" t="inlineStr"/>
@@ -15596,22 +15588,22 @@
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>Fresh Egg Traders</t>
+          <t>Protein Shop</t>
         </is>
       </c>
       <c r="E357" s="9" t="n">
-        <v>1185408</v>
+        <v>147840</v>
       </c>
       <c r="F357" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0904</t>
+          <t>A-INV-EG-27-0903</t>
         </is>
       </c>
       <c r="G357" s="8" t="inlineStr"/>
       <c r="H357" s="8" t="inlineStr"/>
       <c r="I357" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J357" s="10" t="inlineStr"/>
@@ -15634,22 +15626,22 @@
       </c>
       <c r="D358" s="8" t="inlineStr">
         <is>
-          <t>PD Egg Store</t>
+          <t>Fresh Egg Traders</t>
         </is>
       </c>
       <c r="E358" s="9" t="n">
-        <v>531278</v>
+        <v>1185408</v>
       </c>
       <c r="F358" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0905</t>
+          <t>A-INV-EG-27-0904</t>
         </is>
       </c>
       <c r="G358" s="8" t="inlineStr"/>
       <c r="H358" s="8" t="inlineStr"/>
       <c r="I358" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J358" s="10" t="inlineStr"/>
@@ -15667,27 +15659,27 @@
       </c>
       <c r="C359" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>PD Egg Store</t>
         </is>
       </c>
       <c r="E359" s="9" t="n">
-        <v>268800</v>
+        <v>531278</v>
       </c>
       <c r="F359" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0906</t>
+          <t>A-INV-EG-27-0905</t>
         </is>
       </c>
       <c r="G359" s="8" t="inlineStr"/>
       <c r="H359" s="8" t="inlineStr"/>
       <c r="I359" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J359" s="10" t="inlineStr"/>
@@ -15710,7 +15702,7 @@
       </c>
       <c r="D360" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E360" s="9" t="n">
@@ -15718,7 +15710,7 @@
       </c>
       <c r="F360" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0907</t>
+          <t>A-INV-EG-27-0906</t>
         </is>
       </c>
       <c r="G360" s="8" t="inlineStr"/>
@@ -15748,7 +15740,7 @@
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E361" s="9" t="n">
@@ -15756,7 +15748,7 @@
       </c>
       <c r="F361" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0908</t>
+          <t>A-INV-EG-27-0907</t>
         </is>
       </c>
       <c r="G361" s="8" t="inlineStr"/>
@@ -15786,15 +15778,15 @@
       </c>
       <c r="D362" s="8" t="inlineStr">
         <is>
-          <t>Josef Ali</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E362" s="9" t="n">
-        <v>174720</v>
+        <v>268800</v>
       </c>
       <c r="F362" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0909</t>
+          <t>A-INV-EG-27-0908</t>
         </is>
       </c>
       <c r="G362" s="8" t="inlineStr"/>
@@ -15824,7 +15816,7 @@
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>Josef Ali</t>
         </is>
       </c>
       <c r="E363" s="9" t="n">
@@ -15832,7 +15824,7 @@
       </c>
       <c r="F363" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0910</t>
+          <t>A-INV-EG-27-0909</t>
         </is>
       </c>
       <c r="G363" s="8" t="inlineStr"/>
@@ -15857,20 +15849,20 @@
       </c>
       <c r="C364" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D364" s="8" t="inlineStr">
         <is>
-          <t>M/s Mayengbam Enterprises</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E364" s="9" t="n">
-        <v>1209600</v>
+        <v>174720</v>
       </c>
       <c r="F364" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0911</t>
+          <t>A-INV-EG-27-0910</t>
         </is>
       </c>
       <c r="G364" s="8" t="inlineStr"/>
@@ -15900,15 +15892,15 @@
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>M/s Mayengbam Enterprises</t>
         </is>
       </c>
       <c r="E365" s="9" t="n">
-        <v>268800</v>
+        <v>1209600</v>
       </c>
       <c r="F365" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0912</t>
+          <t>A-INV-EG-27-0911</t>
         </is>
       </c>
       <c r="G365" s="8" t="inlineStr"/>
@@ -15938,15 +15930,15 @@
       </c>
       <c r="D366" s="8" t="inlineStr">
         <is>
-          <t>PUYA MARKETING</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E366" s="9" t="n">
-        <v>1241856</v>
+        <v>268800</v>
       </c>
       <c r="F366" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0913</t>
+          <t>A-INV-EG-27-0912</t>
         </is>
       </c>
       <c r="G366" s="8" t="inlineStr"/>
@@ -15976,15 +15968,15 @@
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>PUYA MARKETING</t>
         </is>
       </c>
       <c r="E367" s="9" t="n">
-        <v>268800</v>
+        <v>1241856</v>
       </c>
       <c r="F367" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0914</t>
+          <t>A-INV-EG-27-0913</t>
         </is>
       </c>
       <c r="G367" s="8" t="inlineStr"/>
@@ -16009,7 +16001,7 @@
       </c>
       <c r="C368" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D368" s="8" t="inlineStr">
@@ -16022,7 +16014,7 @@
       </c>
       <c r="F368" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0915</t>
+          <t>A-INV-EG-27-0914</t>
         </is>
       </c>
       <c r="G368" s="8" t="inlineStr"/>
@@ -16052,7 +16044,7 @@
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E369" s="9" t="n">
@@ -16060,7 +16052,7 @@
       </c>
       <c r="F369" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0916</t>
+          <t>A-INV-EG-27-0915</t>
         </is>
       </c>
       <c r="G369" s="8" t="inlineStr"/>
@@ -16090,15 +16082,15 @@
       </c>
       <c r="D370" s="8" t="inlineStr">
         <is>
-          <t>Chowdhury n Sons</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E370" s="9" t="n">
-        <v>1123248</v>
+        <v>268800</v>
       </c>
       <c r="F370" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0917</t>
+          <t>A-INV-EG-27-0916</t>
         </is>
       </c>
       <c r="G370" s="8" t="inlineStr"/>
@@ -16128,15 +16120,15 @@
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>Protein Shop</t>
+          <t>Chowdhury n Sons</t>
         </is>
       </c>
       <c r="E371" s="9" t="n">
-        <v>147840</v>
+        <v>1123248</v>
       </c>
       <c r="F371" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0918</t>
+          <t>A-INV-EG-27-0917</t>
         </is>
       </c>
       <c r="G371" s="8" t="inlineStr"/>
@@ -16166,15 +16158,15 @@
       </c>
       <c r="D372" s="8" t="inlineStr">
         <is>
-          <t>PD Egg Store</t>
+          <t>Protein Shop</t>
         </is>
       </c>
       <c r="E372" s="9" t="n">
-        <v>529683</v>
+        <v>147840</v>
       </c>
       <c r="F372" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0919</t>
+          <t>A-INV-EG-27-0918</t>
         </is>
       </c>
       <c r="G372" s="8" t="inlineStr"/>
@@ -16199,20 +16191,20 @@
       </c>
       <c r="C373" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>PD Egg Store</t>
         </is>
       </c>
       <c r="E373" s="9" t="n">
-        <v>256200</v>
+        <v>529683</v>
       </c>
       <c r="F373" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0920</t>
+          <t>A-INV-EG-27-0919</t>
         </is>
       </c>
       <c r="G373" s="8" t="inlineStr"/>
@@ -16242,15 +16234,15 @@
       </c>
       <c r="D374" s="8" t="inlineStr">
         <is>
-          <t>Zakir Egg Store</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E374" s="9" t="n">
-        <v>1209387</v>
+        <v>256200</v>
       </c>
       <c r="F374" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0921</t>
+          <t>A-INV-EG-27-0920</t>
         </is>
       </c>
       <c r="G374" s="8" t="inlineStr"/>
@@ -16280,15 +16272,15 @@
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Zakir Egg Store</t>
         </is>
       </c>
       <c r="E375" s="9" t="n">
-        <v>256200</v>
+        <v>1209387</v>
       </c>
       <c r="F375" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0922</t>
+          <t>A-INV-EG-27-0921</t>
         </is>
       </c>
       <c r="G375" s="8" t="inlineStr"/>
@@ -16318,15 +16310,15 @@
       </c>
       <c r="D376" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E376" s="9" t="n">
-        <v>166530</v>
+        <v>256200</v>
       </c>
       <c r="F376" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0923</t>
+          <t>A-INV-EG-27-0922</t>
         </is>
       </c>
       <c r="G376" s="8" t="inlineStr"/>
@@ -16356,15 +16348,15 @@
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E377" s="9" t="n">
-        <v>256200</v>
+        <v>166530</v>
       </c>
       <c r="F377" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0924</t>
+          <t>A-INV-EG-27-0923</t>
         </is>
       </c>
       <c r="G377" s="8" t="inlineStr"/>
@@ -16394,15 +16386,15 @@
       </c>
       <c r="D378" s="8" t="inlineStr">
         <is>
-          <t>Fresh Egg Traders</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E378" s="9" t="n">
-        <v>1144676</v>
+        <v>256200</v>
       </c>
       <c r="F378" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0925</t>
+          <t>A-INV-EG-27-0924</t>
         </is>
       </c>
       <c r="G378" s="8" t="inlineStr"/>
@@ -16432,15 +16424,15 @@
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>Sahil Egg Center</t>
+          <t>Fresh Egg Traders</t>
         </is>
       </c>
       <c r="E379" s="9" t="n">
-        <v>577860</v>
+        <v>1144676</v>
       </c>
       <c r="F379" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0926</t>
+          <t>A-INV-EG-27-0925</t>
         </is>
       </c>
       <c r="G379" s="8" t="inlineStr"/>
@@ -16465,20 +16457,20 @@
       </c>
       <c r="C380" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D380" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Sahil Egg Center</t>
         </is>
       </c>
       <c r="E380" s="9" t="n">
-        <v>256200</v>
+        <v>577860</v>
       </c>
       <c r="F380" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0927</t>
+          <t>A-INV-EG-27-0926</t>
         </is>
       </c>
       <c r="G380" s="8" t="inlineStr"/>
@@ -16508,15 +16500,15 @@
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E381" s="9" t="n">
-        <v>409300</v>
+        <v>256200</v>
       </c>
       <c r="F381" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0928</t>
+          <t>A-INV-EG-27-0927</t>
         </is>
       </c>
       <c r="G381" s="8" t="inlineStr"/>
@@ -16546,15 +16538,15 @@
       </c>
       <c r="D382" s="8" t="inlineStr">
         <is>
-          <t>Josef Ali</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E382" s="9" t="n">
-        <v>146695</v>
+        <v>409300</v>
       </c>
       <c r="F382" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0929</t>
+          <t>A-INV-EG-27-0928</t>
         </is>
       </c>
       <c r="G382" s="8" t="inlineStr"/>
@@ -16584,15 +16576,15 @@
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>Josef Ali</t>
         </is>
       </c>
       <c r="E383" s="9" t="n">
-        <v>289670</v>
+        <v>146695</v>
       </c>
       <c r="F383" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0930</t>
+          <t>A-INV-EG-27-0929</t>
         </is>
       </c>
       <c r="G383" s="8" t="inlineStr"/>
@@ -16622,15 +16614,15 @@
       </c>
       <c r="D384" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E384" s="9" t="n">
-        <v>256200</v>
+        <v>289670</v>
       </c>
       <c r="F384" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0931</t>
+          <t>A-INV-EG-27-0930</t>
         </is>
       </c>
       <c r="G384" s="8" t="inlineStr"/>
@@ -16660,15 +16652,15 @@
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>Fariha Store</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E385" s="9" t="n">
-        <v>217150</v>
+        <v>256200</v>
       </c>
       <c r="F385" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0932</t>
+          <t>A-INV-EG-27-0931</t>
         </is>
       </c>
       <c r="G385" s="8" t="inlineStr"/>
@@ -16698,15 +16690,15 @@
       </c>
       <c r="D386" s="8" t="inlineStr">
         <is>
-          <t>Rahman Store</t>
+          <t>Fariha Store</t>
         </is>
       </c>
       <c r="E386" s="9" t="n">
-        <v>1195840</v>
+        <v>217150</v>
       </c>
       <c r="F386" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0933</t>
+          <t>A-INV-EG-27-0932</t>
         </is>
       </c>
       <c r="G386" s="8" t="inlineStr"/>
@@ -16719,88 +16711,88 @@
       <c r="J386" s="10" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B387" s="5" t="inlineStr">
+      <c r="A387" s="8" t="inlineStr">
+        <is>
+          <t>Only in Zoho - import</t>
+        </is>
+      </c>
+      <c r="B387" s="8" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0952</t>
         </is>
       </c>
-      <c r="C387" s="5" t="inlineStr">
+      <c r="C387" s="8" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="D387" s="5" t="inlineStr">
+      <c r="D387" s="8" t="inlineStr">
+        <is>
+          <t>Rahman Store</t>
+        </is>
+      </c>
+      <c r="E387" s="9" t="n">
+        <v>1195840</v>
+      </c>
+      <c r="F387" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0933</t>
+        </is>
+      </c>
+      <c r="G387" s="8" t="inlineStr"/>
+      <c r="H387" s="8" t="inlineStr"/>
+      <c r="I387" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J387" s="10" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B388" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0953</t>
+        </is>
+      </c>
+      <c r="C388" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D388" s="5" t="inlineStr">
         <is>
           <t>Protein Shop</t>
         </is>
       </c>
-      <c r="E387" s="6" t="n">
+      <c r="E388" s="6" t="n">
         <v>153100</v>
       </c>
-      <c r="F387" s="5" t="inlineStr">
+      <c r="F388" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0934</t>
         </is>
       </c>
-      <c r="G387" s="5" t="inlineStr">
+      <c r="G388" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0852</t>
         </is>
       </c>
-      <c r="H387" s="5" t="inlineStr"/>
-      <c r="I387" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J387" s="7" t="inlineStr">
+      <c r="H388" s="5" t="inlineStr"/>
+      <c r="I388" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J388" s="7" t="inlineStr">
         <is>
           <t>Zoho's date is the dispatch day</t>
         </is>
       </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="8" t="inlineStr">
-        <is>
-          <t>Only in Zoho - import</t>
-        </is>
-      </c>
-      <c r="B388" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0953</t>
-        </is>
-      </c>
-      <c r="C388" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="D388" s="8" t="inlineStr">
-        <is>
-          <t>M/s Annapurna Bakery</t>
-        </is>
-      </c>
-      <c r="E388" s="9" t="n">
-        <v>150120</v>
-      </c>
-      <c r="F388" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0935</t>
-        </is>
-      </c>
-      <c r="G388" s="8" t="inlineStr"/>
-      <c r="H388" s="8" t="inlineStr"/>
-      <c r="I388" s="8" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J388" s="10" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="8" t="inlineStr">
@@ -16820,15 +16812,15 @@
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>HKD Egg Traders</t>
+          <t>M/s Annapurna Bakery</t>
         </is>
       </c>
       <c r="E389" s="9" t="n">
-        <v>246760</v>
+        <v>150120</v>
       </c>
       <c r="F389" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0936</t>
+          <t>A-INV-EG-27-0935</t>
         </is>
       </c>
       <c r="G389" s="8" t="inlineStr"/>
@@ -16841,46 +16833,42 @@
       <c r="J389" s="10" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B390" s="5" t="inlineStr">
+      <c r="A390" s="8" t="inlineStr">
+        <is>
+          <t>Only in Zoho - import</t>
+        </is>
+      </c>
+      <c r="B390" s="8" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0955</t>
         </is>
       </c>
-      <c r="C390" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="D390" s="5" t="inlineStr">
-        <is>
-          <t>NB Traders</t>
-        </is>
-      </c>
-      <c r="E390" s="6" t="n">
-        <v>572300</v>
-      </c>
-      <c r="F390" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0937</t>
-        </is>
-      </c>
-      <c r="G390" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0839</t>
-        </is>
-      </c>
-      <c r="H390" s="5" t="inlineStr"/>
-      <c r="I390" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J390" s="7" t="inlineStr"/>
+      <c r="C390" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D390" s="8" t="inlineStr">
+        <is>
+          <t>HKD Egg Traders</t>
+        </is>
+      </c>
+      <c r="E390" s="9" t="n">
+        <v>246760</v>
+      </c>
+      <c r="F390" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0936</t>
+        </is>
+      </c>
+      <c r="G390" s="8" t="inlineStr"/>
+      <c r="H390" s="8" t="inlineStr"/>
+      <c r="I390" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J390" s="10" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="5" t="inlineStr">
@@ -16900,20 +16888,20 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E391" s="6" t="n">
-        <v>283400</v>
+        <v>572300</v>
       </c>
       <c r="F391" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0938</t>
+          <t>A-INV-EG-27-0937</t>
         </is>
       </c>
       <c r="G391" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0838</t>
+          <t>A-INV-EG-27-0839</t>
         </is>
       </c>
       <c r="H391" s="5" t="inlineStr"/>
@@ -16925,84 +16913,84 @@
       <c r="J391" s="7" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="8" t="inlineStr">
+      <c r="A392" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B392" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0957</t>
+        </is>
+      </c>
+      <c r="C392" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D392" s="5" t="inlineStr">
+        <is>
+          <t>Kamakhya Traders</t>
+        </is>
+      </c>
+      <c r="E392" s="6" t="n">
+        <v>283400</v>
+      </c>
+      <c r="F392" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0938</t>
+        </is>
+      </c>
+      <c r="G392" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0838</t>
+        </is>
+      </c>
+      <c r="H392" s="5" t="inlineStr"/>
+      <c r="I392" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J392" s="7" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="8" t="inlineStr">
         <is>
           <t>Only in Zoho - import</t>
         </is>
       </c>
-      <c r="B392" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0957</t>
-        </is>
-      </c>
-      <c r="C392" s="8" t="inlineStr">
+      <c r="B393" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0958</t>
+        </is>
+      </c>
+      <c r="C393" s="8" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="D392" s="8" t="inlineStr">
+      <c r="D393" s="8" t="inlineStr">
         <is>
           <t>PD Egg Store</t>
         </is>
       </c>
-      <c r="E392" s="9" t="n">
+      <c r="E393" s="9" t="n">
         <v>571145</v>
       </c>
-      <c r="F392" s="8" t="inlineStr">
+      <c r="F393" s="8" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0939</t>
         </is>
       </c>
-      <c r="G392" s="8" t="inlineStr"/>
-      <c r="H392" s="8" t="inlineStr"/>
-      <c r="I392" s="8" t="inlineStr">
+      <c r="G393" s="8" t="inlineStr"/>
+      <c r="H393" s="8" t="inlineStr"/>
+      <c r="I393" s="8" t="inlineStr">
         <is>
           <t>overdue</t>
         </is>
       </c>
-      <c r="J392" s="10" t="inlineStr"/>
-    </row>
-    <row r="393">
-      <c r="A393" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B393" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0958</t>
-        </is>
-      </c>
-      <c r="C393" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="D393" s="5" t="inlineStr">
-        <is>
-          <t>SS Food</t>
-        </is>
-      </c>
-      <c r="E393" s="6" t="n">
-        <v>167895</v>
-      </c>
-      <c r="F393" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0940</t>
-        </is>
-      </c>
-      <c r="G393" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0841</t>
-        </is>
-      </c>
-      <c r="H393" s="5" t="inlineStr"/>
-      <c r="I393" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J393" s="7" t="inlineStr"/>
+      <c r="J393" s="10" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="5" t="inlineStr">
@@ -17022,20 +17010,20 @@
       </c>
       <c r="D394" s="5" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E394" s="6" t="n">
-        <v>295800</v>
+        <v>167895</v>
       </c>
       <c r="F394" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0941</t>
+          <t>A-INV-EG-27-0940</t>
         </is>
       </c>
       <c r="G394" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0840</t>
+          <t>A-INV-EG-27-0841</t>
         </is>
       </c>
       <c r="H394" s="5" t="inlineStr"/>
@@ -17047,80 +17035,84 @@
       <c r="J394" s="7" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="11" t="inlineStr">
+      <c r="A395" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B395" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0960</t>
+        </is>
+      </c>
+      <c r="C395" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D395" s="5" t="inlineStr">
+        <is>
+          <t>Tapan Saha</t>
+        </is>
+      </c>
+      <c r="E395" s="6" t="n">
+        <v>295800</v>
+      </c>
+      <c r="F395" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0941</t>
+        </is>
+      </c>
+      <c r="G395" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0840</t>
+        </is>
+      </c>
+      <c r="H395" s="5" t="inlineStr"/>
+      <c r="I395" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J395" s="7" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="11" t="inlineStr">
         <is>
           <t>Only in niko - keep</t>
         </is>
       </c>
-      <c r="B395" s="11" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0960</t>
-        </is>
-      </c>
-      <c r="C395" s="11" t="inlineStr">
+      <c r="B396" s="11" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0961</t>
+        </is>
+      </c>
+      <c r="C396" s="11" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="D395" s="11" t="inlineStr">
+      <c r="D396" s="11" t="inlineStr">
         <is>
           <t>PD Egg Store</t>
         </is>
       </c>
-      <c r="E395" s="12" t="n">
+      <c r="E396" s="12" t="n">
         <v>548538</v>
       </c>
-      <c r="F395" s="11" t="inlineStr"/>
-      <c r="G395" s="11" t="inlineStr">
+      <c r="F396" s="11" t="inlineStr"/>
+      <c r="G396" s="11" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0837</t>
         </is>
       </c>
-      <c r="H395" s="11" t="inlineStr"/>
-      <c r="I395" s="11" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J395" s="13" t="inlineStr"/>
-    </row>
-    <row r="396">
-      <c r="A396" s="8" t="inlineStr">
-        <is>
-          <t>Only in Zoho - import</t>
-        </is>
-      </c>
-      <c r="B396" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0961</t>
-        </is>
-      </c>
-      <c r="C396" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="D396" s="8" t="inlineStr">
-        <is>
-          <t>Fresh Egg Traders</t>
-        </is>
-      </c>
-      <c r="E396" s="9" t="n">
-        <v>1167320</v>
-      </c>
-      <c r="F396" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0942</t>
-        </is>
-      </c>
-      <c r="G396" s="8" t="inlineStr"/>
-      <c r="H396" s="8" t="inlineStr"/>
-      <c r="I396" s="8" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J396" s="10" t="inlineStr"/>
+      <c r="H396" s="11" t="inlineStr"/>
+      <c r="I396" s="11" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J396" s="13" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="8" t="inlineStr">
@@ -17140,22 +17132,22 @@
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>DN Store</t>
+          <t>Fresh Egg Traders</t>
         </is>
       </c>
       <c r="E397" s="9" t="n">
-        <v>279070</v>
+        <v>1167320</v>
       </c>
       <c r="F397" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0943</t>
+          <t>A-INV-EG-27-0942</t>
         </is>
       </c>
       <c r="G397" s="8" t="inlineStr"/>
       <c r="H397" s="8" t="inlineStr"/>
       <c r="I397" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J397" s="10" t="inlineStr"/>
@@ -17178,15 +17170,15 @@
       </c>
       <c r="D398" s="8" t="inlineStr">
         <is>
-          <t>DG Egg Point (Debajeet Gogoi)</t>
+          <t>DN Store</t>
         </is>
       </c>
       <c r="E398" s="9" t="n">
-        <v>295060</v>
+        <v>279070</v>
       </c>
       <c r="F398" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0944</t>
+          <t>A-INV-EG-27-0943</t>
         </is>
       </c>
       <c r="G398" s="8" t="inlineStr"/>
@@ -17199,46 +17191,42 @@
       <c r="J398" s="10" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B399" s="5" t="inlineStr">
+      <c r="A399" s="8" t="inlineStr">
+        <is>
+          <t>Only in Zoho - import</t>
+        </is>
+      </c>
+      <c r="B399" s="8" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0964</t>
         </is>
       </c>
-      <c r="C399" s="5" t="inlineStr">
+      <c r="C399" s="8" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D399" s="5" t="inlineStr">
-        <is>
-          <t>Kamakhya Traders</t>
-        </is>
-      </c>
-      <c r="E399" s="6" t="n">
-        <v>262013</v>
-      </c>
-      <c r="F399" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0945</t>
-        </is>
-      </c>
-      <c r="G399" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0854</t>
-        </is>
-      </c>
-      <c r="H399" s="5" t="inlineStr"/>
-      <c r="I399" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J399" s="7" t="inlineStr"/>
+      <c r="D399" s="8" t="inlineStr">
+        <is>
+          <t>DG Egg Point (Debajeet Gogoi)</t>
+        </is>
+      </c>
+      <c r="E399" s="9" t="n">
+        <v>295060</v>
+      </c>
+      <c r="F399" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0944</t>
+        </is>
+      </c>
+      <c r="G399" s="8" t="inlineStr"/>
+      <c r="H399" s="8" t="inlineStr"/>
+      <c r="I399" s="8" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="J399" s="10" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="5" t="inlineStr">
@@ -17258,7 +17246,7 @@
       </c>
       <c r="D400" s="5" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E400" s="6" t="n">
@@ -17266,12 +17254,12 @@
       </c>
       <c r="F400" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0946</t>
+          <t>A-INV-EG-27-0945</t>
         </is>
       </c>
       <c r="G400" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0856</t>
+          <t>A-INV-EG-27-0854</t>
         </is>
       </c>
       <c r="H400" s="5" t="inlineStr"/>
@@ -17283,42 +17271,46 @@
       <c r="J400" s="7" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="8" t="inlineStr">
-        <is>
-          <t>Only in Zoho - import</t>
-        </is>
-      </c>
-      <c r="B401" s="8" t="inlineStr">
+      <c r="A401" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B401" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0966</t>
         </is>
       </c>
-      <c r="C401" s="8" t="inlineStr">
+      <c r="C401" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D401" s="8" t="inlineStr">
-        <is>
-          <t>Protein Shop</t>
-        </is>
-      </c>
-      <c r="E401" s="9" t="n">
-        <v>154200</v>
-      </c>
-      <c r="F401" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0947</t>
-        </is>
-      </c>
-      <c r="G401" s="8" t="inlineStr"/>
-      <c r="H401" s="8" t="inlineStr"/>
-      <c r="I401" s="8" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="J401" s="10" t="inlineStr"/>
+      <c r="D401" s="5" t="inlineStr">
+        <is>
+          <t>NB Traders</t>
+        </is>
+      </c>
+      <c r="E401" s="6" t="n">
+        <v>262013</v>
+      </c>
+      <c r="F401" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0946</t>
+        </is>
+      </c>
+      <c r="G401" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0856</t>
+        </is>
+      </c>
+      <c r="H401" s="5" t="inlineStr"/>
+      <c r="I401" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J401" s="7" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="8" t="inlineStr">
@@ -17338,22 +17330,22 @@
       </c>
       <c r="D402" s="8" t="inlineStr">
         <is>
-          <t>PUYA MARKETING</t>
+          <t>Protein Shop</t>
         </is>
       </c>
       <c r="E402" s="9" t="n">
-        <v>1210600</v>
+        <v>154200</v>
       </c>
       <c r="F402" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0948</t>
+          <t>A-INV-EG-27-0947</t>
         </is>
       </c>
       <c r="G402" s="8" t="inlineStr"/>
       <c r="H402" s="8" t="inlineStr"/>
       <c r="I402" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J402" s="10" t="inlineStr"/>
@@ -17376,63 +17368,63 @@
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>PUYA MARKETING</t>
         </is>
       </c>
       <c r="E403" s="9" t="n">
-        <v>417800</v>
+        <v>1210600</v>
       </c>
       <c r="F403" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0949</t>
+          <t>A-INV-EG-27-0948</t>
         </is>
       </c>
       <c r="G403" s="8" t="inlineStr"/>
       <c r="H403" s="8" t="inlineStr"/>
       <c r="I403" s="8" t="inlineStr">
         <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J403" s="10" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="8" t="inlineStr">
+        <is>
+          <t>Only in Zoho - import</t>
+        </is>
+      </c>
+      <c r="B404" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0969</t>
+        </is>
+      </c>
+      <c r="C404" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D404" s="8" t="inlineStr">
+        <is>
+          <t>Tapan Saha</t>
+        </is>
+      </c>
+      <c r="E404" s="9" t="n">
+        <v>417800</v>
+      </c>
+      <c r="F404" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0949</t>
+        </is>
+      </c>
+      <c r="G404" s="8" t="inlineStr"/>
+      <c r="H404" s="8" t="inlineStr"/>
+      <c r="I404" s="8" t="inlineStr">
+        <is>
           <t>overdue</t>
         </is>
       </c>
-      <c r="J403" s="10" t="inlineStr"/>
-    </row>
-    <row r="404">
-      <c r="A404" s="11" t="inlineStr">
-        <is>
-          <t>Only in niko - keep</t>
-        </is>
-      </c>
-      <c r="B404" s="11" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0969</t>
-        </is>
-      </c>
-      <c r="C404" s="11" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="D404" s="11" t="inlineStr">
-        <is>
-          <t>M/s Puya</t>
-        </is>
-      </c>
-      <c r="E404" s="12" t="n">
-        <v>1190325</v>
-      </c>
-      <c r="F404" s="11" t="inlineStr"/>
-      <c r="G404" s="11" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0842</t>
-        </is>
-      </c>
-      <c r="H404" s="11" t="inlineStr"/>
-      <c r="I404" s="11" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J404" s="13" t="inlineStr"/>
+      <c r="J404" s="10" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="11" t="inlineStr">
@@ -17452,16 +17444,16 @@
       </c>
       <c r="D405" s="11" t="inlineStr">
         <is>
-          <t>Fresh Egg Traders</t>
+          <t>M/s Puya</t>
         </is>
       </c>
       <c r="E405" s="12" t="n">
-        <v>1156965</v>
+        <v>1190325</v>
       </c>
       <c r="F405" s="11" t="inlineStr"/>
       <c r="G405" s="11" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0850</t>
+          <t>A-INV-EG-27-0842</t>
         </is>
       </c>
       <c r="H405" s="11" t="inlineStr"/>
@@ -17490,16 +17482,16 @@
       </c>
       <c r="D406" s="11" t="inlineStr">
         <is>
-          <t>DN Store</t>
+          <t>Fresh Egg Traders</t>
         </is>
       </c>
       <c r="E406" s="12" t="n">
-        <v>276015</v>
+        <v>1156965</v>
       </c>
       <c r="F406" s="11" t="inlineStr"/>
       <c r="G406" s="11" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0851</t>
+          <t>A-INV-EG-27-0850</t>
         </is>
       </c>
       <c r="H406" s="11" t="inlineStr"/>
@@ -17528,16 +17520,16 @@
       </c>
       <c r="D407" s="11" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>DN Store</t>
         </is>
       </c>
       <c r="E407" s="12" t="n">
-        <v>415163</v>
+        <v>276015</v>
       </c>
       <c r="F407" s="11" t="inlineStr"/>
       <c r="G407" s="11" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0853</t>
+          <t>A-INV-EG-27-0851</t>
         </is>
       </c>
       <c r="H407" s="11" t="inlineStr"/>
@@ -17566,16 +17558,16 @@
       </c>
       <c r="D408" s="11" t="inlineStr">
         <is>
-          <t>DG Egg Point</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E408" s="12" t="n">
-        <v>292470</v>
+        <v>415163</v>
       </c>
       <c r="F408" s="11" t="inlineStr"/>
       <c r="G408" s="11" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0855</t>
+          <t>A-INV-EG-27-0853</t>
         </is>
       </c>
       <c r="H408" s="11" t="inlineStr"/>
@@ -17587,46 +17579,42 @@
       <c r="J408" s="13" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B409" s="5" t="inlineStr">
+      <c r="A409" s="11" t="inlineStr">
+        <is>
+          <t>Only in niko - keep</t>
+        </is>
+      </c>
+      <c r="B409" s="11" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0974</t>
         </is>
       </c>
-      <c r="C409" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="D409" s="5" t="inlineStr">
-        <is>
-          <t>Tapan Saha</t>
-        </is>
-      </c>
-      <c r="E409" s="6" t="n">
-        <v>263850</v>
-      </c>
-      <c r="F409" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0950</t>
-        </is>
-      </c>
-      <c r="G409" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0843</t>
-        </is>
-      </c>
-      <c r="H409" s="5" t="inlineStr"/>
-      <c r="I409" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J409" s="7" t="inlineStr"/>
+      <c r="C409" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D409" s="11" t="inlineStr">
+        <is>
+          <t>DG Egg Point</t>
+        </is>
+      </c>
+      <c r="E409" s="12" t="n">
+        <v>292470</v>
+      </c>
+      <c r="F409" s="11" t="inlineStr"/>
+      <c r="G409" s="11" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0855</t>
+        </is>
+      </c>
+      <c r="H409" s="11" t="inlineStr"/>
+      <c r="I409" s="11" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J409" s="13" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="5" t="inlineStr">
@@ -17646,20 +17634,20 @@
       </c>
       <c r="D410" s="5" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E410" s="6" t="n">
-        <v>91140</v>
+        <v>263850</v>
       </c>
       <c r="F410" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0951</t>
+          <t>A-INV-EG-27-0950</t>
         </is>
       </c>
       <c r="G410" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0844</t>
+          <t>A-INV-EG-27-0843</t>
         </is>
       </c>
       <c r="H410" s="5" t="inlineStr"/>
@@ -17688,20 +17676,20 @@
       </c>
       <c r="D411" s="5" t="inlineStr">
         <is>
-          <t>Josef Ali</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E411" s="6" t="n">
-        <v>167220</v>
+        <v>91140</v>
       </c>
       <c r="F411" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0952</t>
+          <t>A-INV-EG-27-0951</t>
         </is>
       </c>
       <c r="G411" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0845</t>
+          <t>A-INV-EG-27-0844</t>
         </is>
       </c>
       <c r="H411" s="5" t="inlineStr"/>
@@ -17713,84 +17701,84 @@
       <c r="J411" s="7" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="8" t="inlineStr">
+      <c r="A412" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B412" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0977</t>
+        </is>
+      </c>
+      <c r="C412" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D412" s="5" t="inlineStr">
+        <is>
+          <t>Josef Ali</t>
+        </is>
+      </c>
+      <c r="E412" s="6" t="n">
+        <v>167220</v>
+      </c>
+      <c r="F412" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0952</t>
+        </is>
+      </c>
+      <c r="G412" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0845</t>
+        </is>
+      </c>
+      <c r="H412" s="5" t="inlineStr"/>
+      <c r="I412" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J412" s="7" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="8" t="inlineStr">
         <is>
           <t>Only in Zoho - import</t>
         </is>
       </c>
-      <c r="B412" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0977</t>
-        </is>
-      </c>
-      <c r="C412" s="8" t="inlineStr">
+      <c r="B413" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0978</t>
+        </is>
+      </c>
+      <c r="C413" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="D412" s="8" t="inlineStr">
+      <c r="D413" s="8" t="inlineStr">
         <is>
           <t>Kamakhya Traders</t>
         </is>
       </c>
-      <c r="E412" s="9" t="n">
+      <c r="E413" s="9" t="n">
         <v>254663</v>
       </c>
-      <c r="F412" s="8" t="inlineStr">
+      <c r="F413" s="8" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0953</t>
         </is>
       </c>
-      <c r="G412" s="8" t="inlineStr"/>
-      <c r="H412" s="8" t="inlineStr"/>
-      <c r="I412" s="8" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J412" s="10" t="inlineStr"/>
-    </row>
-    <row r="413">
-      <c r="A413" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B413" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0978</t>
-        </is>
-      </c>
-      <c r="C413" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="D413" s="5" t="inlineStr">
-        <is>
-          <t>NB Traders</t>
-        </is>
-      </c>
-      <c r="E413" s="6" t="n">
-        <v>263850</v>
-      </c>
-      <c r="F413" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0954</t>
-        </is>
-      </c>
-      <c r="G413" s="5" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0849</t>
-        </is>
-      </c>
-      <c r="H413" s="5" t="inlineStr"/>
-      <c r="I413" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J413" s="7" t="inlineStr"/>
+      <c r="G413" s="8" t="inlineStr"/>
+      <c r="H413" s="8" t="inlineStr"/>
+      <c r="I413" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J413" s="10" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="5" t="inlineStr">
@@ -17810,20 +17798,20 @@
       </c>
       <c r="D414" s="5" t="inlineStr">
         <is>
-          <t>Chowdhury n Sons</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E414" s="6" t="n">
-        <v>896400</v>
+        <v>263850</v>
       </c>
       <c r="F414" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0955</t>
+          <t>A-INV-EG-27-0954</t>
         </is>
       </c>
       <c r="G414" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0847</t>
+          <t>A-INV-EG-27-0849</t>
         </is>
       </c>
       <c r="H414" s="5" t="inlineStr"/>
@@ -17852,20 +17840,20 @@
       </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>M/s Mayengbam Enterprises</t>
+          <t>Chowdhury n Sons</t>
         </is>
       </c>
       <c r="E415" s="6" t="n">
-        <v>1224564</v>
+        <v>896400</v>
       </c>
       <c r="F415" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0956</t>
+          <t>A-INV-EG-27-0955</t>
         </is>
       </c>
       <c r="G415" s="5" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0848</t>
+          <t>A-INV-EG-27-0847</t>
         </is>
       </c>
       <c r="H415" s="5" t="inlineStr"/>
@@ -17877,80 +17865,84 @@
       <c r="J415" s="7" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="11" t="inlineStr">
+      <c r="A416" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B416" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0981</t>
+        </is>
+      </c>
+      <c r="C416" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D416" s="5" t="inlineStr">
+        <is>
+          <t>M/s Mayengbam Enterprises</t>
+        </is>
+      </c>
+      <c r="E416" s="6" t="n">
+        <v>1224564</v>
+      </c>
+      <c r="F416" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0956</t>
+        </is>
+      </c>
+      <c r="G416" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0848</t>
+        </is>
+      </c>
+      <c r="H416" s="5" t="inlineStr"/>
+      <c r="I416" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J416" s="7" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="11" t="inlineStr">
         <is>
           <t>Only in niko - keep</t>
         </is>
       </c>
-      <c r="B416" s="11" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0981</t>
-        </is>
-      </c>
-      <c r="C416" s="11" t="inlineStr">
+      <c r="B417" s="11" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0982</t>
+        </is>
+      </c>
+      <c r="C417" s="11" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="D416" s="11" t="inlineStr">
+      <c r="D417" s="11" t="inlineStr">
         <is>
           <t>Kamakhya Traders</t>
         </is>
       </c>
-      <c r="E416" s="12" t="n">
+      <c r="E417" s="12" t="n">
         <v>263850</v>
       </c>
-      <c r="F416" s="11" t="inlineStr"/>
-      <c r="G416" s="11" t="inlineStr">
+      <c r="F417" s="11" t="inlineStr"/>
+      <c r="G417" s="11" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0846</t>
         </is>
       </c>
-      <c r="H416" s="11" t="inlineStr"/>
-      <c r="I416" s="11" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J416" s="13" t="inlineStr"/>
-    </row>
-    <row r="417">
-      <c r="A417" s="8" t="inlineStr">
-        <is>
-          <t>Only in Zoho - import</t>
-        </is>
-      </c>
-      <c r="B417" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0982</t>
-        </is>
-      </c>
-      <c r="C417" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="D417" s="8" t="inlineStr">
-        <is>
-          <t>Kamakhya Traders</t>
-        </is>
-      </c>
-      <c r="E417" s="9" t="n">
-        <v>131250</v>
-      </c>
-      <c r="F417" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0957</t>
-        </is>
-      </c>
-      <c r="G417" s="8" t="inlineStr"/>
-      <c r="H417" s="8" t="inlineStr"/>
-      <c r="I417" s="8" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J417" s="10" t="inlineStr"/>
+      <c r="H417" s="11" t="inlineStr"/>
+      <c r="I417" s="11" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J417" s="13" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="8" t="inlineStr">
@@ -17970,22 +17962,22 @@
       </c>
       <c r="D418" s="8" t="inlineStr">
         <is>
-          <t>PD Egg Store</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E418" s="9" t="n">
-        <v>615450</v>
+        <v>131250</v>
       </c>
       <c r="F418" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0958</t>
+          <t>A-INV-EG-27-0957</t>
         </is>
       </c>
       <c r="G418" s="8" t="inlineStr"/>
       <c r="H418" s="8" t="inlineStr"/>
       <c r="I418" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J418" s="10" t="inlineStr"/>
@@ -18008,15 +18000,15 @@
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>PD Egg Store</t>
         </is>
       </c>
       <c r="E419" s="9" t="n">
-        <v>152300</v>
+        <v>615450</v>
       </c>
       <c r="F419" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0959</t>
+          <t>A-INV-EG-27-0958</t>
         </is>
       </c>
       <c r="G419" s="8" t="inlineStr"/>
@@ -18046,22 +18038,22 @@
       </c>
       <c r="D420" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E420" s="9" t="n">
-        <v>185625</v>
+        <v>152300</v>
       </c>
       <c r="F420" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0960</t>
+          <t>A-INV-EG-27-0959</t>
         </is>
       </c>
       <c r="G420" s="8" t="inlineStr"/>
       <c r="H420" s="8" t="inlineStr"/>
       <c r="I420" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J420" s="10" t="inlineStr"/>
@@ -18084,22 +18076,22 @@
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>Zakir Egg Store</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E421" s="9" t="n">
-        <v>1186100</v>
+        <v>185625</v>
       </c>
       <c r="F421" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0961</t>
+          <t>A-INV-EG-27-0960</t>
         </is>
       </c>
       <c r="G421" s="8" t="inlineStr"/>
       <c r="H421" s="8" t="inlineStr"/>
       <c r="I421" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J421" s="10" t="inlineStr"/>
@@ -18122,15 +18114,15 @@
       </c>
       <c r="D422" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Zakir Egg Store</t>
         </is>
       </c>
       <c r="E422" s="9" t="n">
-        <v>152300</v>
+        <v>1186100</v>
       </c>
       <c r="F422" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0962</t>
+          <t>A-INV-EG-27-0961</t>
         </is>
       </c>
       <c r="G422" s="8" t="inlineStr"/>
@@ -18160,15 +18152,15 @@
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>Sahil Egg Center</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E423" s="9" t="n">
-        <v>578400</v>
+        <v>152300</v>
       </c>
       <c r="F423" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0963</t>
+          <t>A-INV-EG-27-0962</t>
         </is>
       </c>
       <c r="G423" s="8" t="inlineStr"/>
@@ -18193,110 +18185,110 @@
       </c>
       <c r="C424" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D424" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>Sahil Egg Center</t>
         </is>
       </c>
       <c r="E424" s="9" t="n">
-        <v>304290</v>
+        <v>578400</v>
       </c>
       <c r="F424" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0964</t>
+          <t>A-INV-EG-27-0963</t>
         </is>
       </c>
       <c r="G424" s="8" t="inlineStr"/>
       <c r="H424" s="8" t="inlineStr"/>
       <c r="I424" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J424" s="10" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="5" t="inlineStr">
-        <is>
-          <t>In both books - renumbered</t>
-        </is>
-      </c>
-      <c r="B425" s="5" t="inlineStr">
+      <c r="A425" s="8" t="inlineStr">
+        <is>
+          <t>Only in Zoho - import</t>
+        </is>
+      </c>
+      <c r="B425" s="8" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0990</t>
         </is>
       </c>
-      <c r="C425" s="5" t="inlineStr">
+      <c r="C425" s="8" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="D425" s="5" t="inlineStr">
+      <c r="D425" s="8" t="inlineStr">
+        <is>
+          <t>SS Food</t>
+        </is>
+      </c>
+      <c r="E425" s="9" t="n">
+        <v>304290</v>
+      </c>
+      <c r="F425" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0964</t>
+        </is>
+      </c>
+      <c r="G425" s="8" t="inlineStr"/>
+      <c r="H425" s="8" t="inlineStr"/>
+      <c r="I425" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J425" s="10" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="5" t="inlineStr">
+        <is>
+          <t>In both books - renumbered</t>
+        </is>
+      </c>
+      <c r="B426" s="5" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0991</t>
+        </is>
+      </c>
+      <c r="C426" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D426" s="5" t="inlineStr">
         <is>
           <t>Tapan Saha</t>
         </is>
       </c>
-      <c r="E425" s="6" t="n">
+      <c r="E426" s="6" t="n">
         <v>396900</v>
       </c>
-      <c r="F425" s="5" t="inlineStr">
+      <c r="F426" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0965</t>
         </is>
       </c>
-      <c r="G425" s="5" t="inlineStr">
+      <c r="G426" s="5" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0857</t>
         </is>
       </c>
-      <c r="H425" s="5" t="inlineStr"/>
-      <c r="I425" s="5" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J425" s="7" t="inlineStr"/>
-    </row>
-    <row r="426">
-      <c r="A426" s="8" t="inlineStr">
-        <is>
-          <t>Only in Zoho - import</t>
-        </is>
-      </c>
-      <c r="B426" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0991</t>
-        </is>
-      </c>
-      <c r="C426" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="D426" s="8" t="inlineStr">
-        <is>
-          <t>NB Traders</t>
-        </is>
-      </c>
-      <c r="E426" s="9" t="n">
-        <v>413700</v>
-      </c>
-      <c r="F426" s="8" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0966</t>
-        </is>
-      </c>
-      <c r="G426" s="8" t="inlineStr"/>
-      <c r="H426" s="8" t="inlineStr"/>
-      <c r="I426" s="8" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="J426" s="10" t="inlineStr"/>
+      <c r="H426" s="5" t="inlineStr"/>
+      <c r="I426" s="5" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J426" s="7" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="8" t="inlineStr">
@@ -18316,22 +18308,22 @@
       </c>
       <c r="D427" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E427" s="9" t="n">
-        <v>454500</v>
+        <v>413700</v>
       </c>
       <c r="F427" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0967</t>
+          <t>A-INV-EG-27-0966</t>
         </is>
       </c>
       <c r="G427" s="8" t="inlineStr"/>
       <c r="H427" s="8" t="inlineStr"/>
       <c r="I427" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J427" s="10" t="inlineStr"/>
@@ -18354,22 +18346,22 @@
       </c>
       <c r="D428" s="8" t="inlineStr">
         <is>
-          <t>Protein Shop</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E428" s="9" t="n">
-        <v>145530</v>
+        <v>454500</v>
       </c>
       <c r="F428" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0968</t>
+          <t>A-INV-EG-27-0967</t>
         </is>
       </c>
       <c r="G428" s="8" t="inlineStr"/>
       <c r="H428" s="8" t="inlineStr"/>
       <c r="I428" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J428" s="10" t="inlineStr"/>
@@ -18392,22 +18384,22 @@
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>Protein Shop</t>
         </is>
       </c>
       <c r="E429" s="9" t="n">
-        <v>171990</v>
+        <v>145530</v>
       </c>
       <c r="F429" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0969</t>
+          <t>A-INV-EG-27-0968</t>
         </is>
       </c>
       <c r="G429" s="8" t="inlineStr"/>
       <c r="H429" s="8" t="inlineStr"/>
       <c r="I429" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J429" s="10" t="inlineStr"/>
@@ -18425,7 +18417,7 @@
       </c>
       <c r="C430" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D430" s="8" t="inlineStr">
@@ -18434,11 +18426,11 @@
         </is>
       </c>
       <c r="E430" s="9" t="n">
-        <v>412050</v>
+        <v>171990</v>
       </c>
       <c r="F430" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0970</t>
+          <t>A-INV-EG-27-0969</t>
         </is>
       </c>
       <c r="G430" s="8" t="inlineStr"/>
@@ -18468,22 +18460,22 @@
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E431" s="9" t="n">
-        <v>402850</v>
+        <v>412050</v>
       </c>
       <c r="F431" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0971</t>
+          <t>A-INV-EG-27-0970</t>
         </is>
       </c>
       <c r="G431" s="8" t="inlineStr"/>
       <c r="H431" s="8" t="inlineStr"/>
       <c r="I431" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J431" s="10" t="inlineStr"/>
@@ -18506,15 +18498,15 @@
       </c>
       <c r="D432" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E432" s="9" t="n">
-        <v>269450</v>
+        <v>402850</v>
       </c>
       <c r="F432" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0972</t>
+          <t>A-INV-EG-27-0971</t>
         </is>
       </c>
       <c r="G432" s="8" t="inlineStr"/>
@@ -18544,22 +18536,22 @@
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E433" s="9" t="n">
-        <v>269363</v>
+        <v>269450</v>
       </c>
       <c r="F433" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0973</t>
+          <t>A-INV-EG-27-0972</t>
         </is>
       </c>
       <c r="G433" s="8" t="inlineStr"/>
       <c r="H433" s="8" t="inlineStr"/>
       <c r="I433" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J433" s="10" t="inlineStr"/>
@@ -18582,15 +18574,15 @@
       </c>
       <c r="D434" s="8" t="inlineStr">
         <is>
-          <t>M/s Annapurna Bakery</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E434" s="9" t="n">
-        <v>84240</v>
+        <v>269363</v>
       </c>
       <c r="F434" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0974</t>
+          <t>A-INV-EG-27-0973</t>
         </is>
       </c>
       <c r="G434" s="8" t="inlineStr"/>
@@ -18615,20 +18607,20 @@
       </c>
       <c r="C435" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>PD Egg Store</t>
+          <t>M/s Annapurna Bakery</t>
         </is>
       </c>
       <c r="E435" s="9" t="n">
-        <v>566985</v>
+        <v>84240</v>
       </c>
       <c r="F435" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0975</t>
+          <t>A-INV-EG-27-0974</t>
         </is>
       </c>
       <c r="G435" s="8" t="inlineStr"/>
@@ -18658,22 +18650,22 @@
       </c>
       <c r="D436" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>PD Egg Store</t>
         </is>
       </c>
       <c r="E436" s="9" t="n">
-        <v>406350</v>
+        <v>566985</v>
       </c>
       <c r="F436" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0976</t>
+          <t>A-INV-EG-27-0975</t>
         </is>
       </c>
       <c r="G436" s="8" t="inlineStr"/>
       <c r="H436" s="8" t="inlineStr"/>
       <c r="I436" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J436" s="10" t="inlineStr"/>
@@ -18696,22 +18688,22 @@
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E437" s="9" t="n">
-        <v>273038</v>
+        <v>406350</v>
       </c>
       <c r="F437" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0977</t>
+          <t>A-INV-EG-27-0976</t>
         </is>
       </c>
       <c r="G437" s="8" t="inlineStr"/>
       <c r="H437" s="8" t="inlineStr"/>
       <c r="I437" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J437" s="10" t="inlineStr"/>
@@ -18734,15 +18726,15 @@
       </c>
       <c r="D438" s="8" t="inlineStr">
         <is>
-          <t>Protein Shop</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E438" s="9" t="n">
-        <v>160995</v>
+        <v>273038</v>
       </c>
       <c r="F438" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0978</t>
+          <t>A-INV-EG-27-0977</t>
         </is>
       </c>
       <c r="G438" s="8" t="inlineStr"/>
@@ -18772,15 +18764,15 @@
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>Sahil Egg Center</t>
+          <t>Protein Shop</t>
         </is>
       </c>
       <c r="E439" s="9" t="n">
-        <v>578400</v>
+        <v>160995</v>
       </c>
       <c r="F439" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0979</t>
+          <t>A-INV-EG-27-0978</t>
         </is>
       </c>
       <c r="G439" s="8" t="inlineStr"/>
@@ -18810,15 +18802,15 @@
       </c>
       <c r="D440" s="8" t="inlineStr">
         <is>
-          <t>Sayedur Rahman</t>
+          <t>Sahil Egg Center</t>
         </is>
       </c>
       <c r="E440" s="9" t="n">
-        <v>264720</v>
+        <v>578400</v>
       </c>
       <c r="F440" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0980</t>
+          <t>A-INV-EG-27-0979</t>
         </is>
       </c>
       <c r="G440" s="8" t="inlineStr"/>
@@ -18848,15 +18840,15 @@
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>Josef Ali</t>
+          <t>Sayedur Rahman</t>
         </is>
       </c>
       <c r="E441" s="9" t="n">
-        <v>174540</v>
+        <v>264720</v>
       </c>
       <c r="F441" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0981</t>
+          <t>A-INV-EG-27-0980</t>
         </is>
       </c>
       <c r="G441" s="8" t="inlineStr"/>
@@ -18886,15 +18878,15 @@
       </c>
       <c r="D442" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>Josef Ali</t>
         </is>
       </c>
       <c r="E442" s="9" t="n">
-        <v>306900</v>
+        <v>174540</v>
       </c>
       <c r="F442" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0982</t>
+          <t>A-INV-EG-27-0981</t>
         </is>
       </c>
       <c r="G442" s="8" t="inlineStr"/>
@@ -18924,15 +18916,15 @@
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E443" s="9" t="n">
-        <v>269955</v>
+        <v>306900</v>
       </c>
       <c r="F443" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0983</t>
+          <t>A-INV-EG-27-0982</t>
         </is>
       </c>
       <c r="G443" s="8" t="inlineStr"/>
@@ -18957,20 +18949,20 @@
       </c>
       <c r="C444" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D444" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E444" s="9" t="n">
-        <v>275100</v>
+        <v>269955</v>
       </c>
       <c r="F444" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0984</t>
+          <t>A-INV-EG-27-0983</t>
         </is>
       </c>
       <c r="G444" s="8" t="inlineStr"/>
@@ -19000,7 +18992,7 @@
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E445" s="9" t="n">
@@ -19008,7 +19000,7 @@
       </c>
       <c r="F445" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0985</t>
+          <t>A-INV-EG-27-0984</t>
         </is>
       </c>
       <c r="G445" s="8" t="inlineStr"/>
@@ -19038,15 +19030,15 @@
       </c>
       <c r="D446" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E446" s="9" t="n">
-        <v>178815</v>
+        <v>275100</v>
       </c>
       <c r="F446" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0986</t>
+          <t>A-INV-EG-27-0985</t>
         </is>
       </c>
       <c r="G446" s="8" t="inlineStr"/>
@@ -19076,15 +19068,15 @@
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E447" s="9" t="n">
-        <v>275100</v>
+        <v>178815</v>
       </c>
       <c r="F447" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0987</t>
+          <t>A-INV-EG-27-0986</t>
         </is>
       </c>
       <c r="G447" s="8" t="inlineStr"/>
@@ -19114,15 +19106,15 @@
       </c>
       <c r="D448" s="8" t="inlineStr">
         <is>
-          <t>Rahman Store</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E448" s="9" t="n">
-        <v>566325</v>
+        <v>275100</v>
       </c>
       <c r="F448" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0988</t>
+          <t>A-INV-EG-27-0987</t>
         </is>
       </c>
       <c r="G448" s="8" t="inlineStr"/>
@@ -19147,20 +19139,20 @@
       </c>
       <c r="C449" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D449" s="8" t="inlineStr">
         <is>
-          <t>DN Store</t>
+          <t>Rahman Store</t>
         </is>
       </c>
       <c r="E449" s="9" t="n">
-        <v>280080</v>
+        <v>566325</v>
       </c>
       <c r="F449" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0989</t>
+          <t>A-INV-EG-27-0988</t>
         </is>
       </c>
       <c r="G449" s="8" t="inlineStr"/>
@@ -19190,15 +19182,15 @@
       </c>
       <c r="D450" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>DN Store</t>
         </is>
       </c>
       <c r="E450" s="9" t="n">
-        <v>275100</v>
+        <v>280080</v>
       </c>
       <c r="F450" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0990</t>
+          <t>A-INV-EG-27-0989</t>
         </is>
       </c>
       <c r="G450" s="8" t="inlineStr"/>
@@ -19228,7 +19220,7 @@
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E451" s="9" t="n">
@@ -19236,7 +19228,7 @@
       </c>
       <c r="F451" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0991</t>
+          <t>A-INV-EG-27-0990</t>
         </is>
       </c>
       <c r="G451" s="8" t="inlineStr"/>
@@ -19266,7 +19258,7 @@
       </c>
       <c r="D452" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E452" s="9" t="n">
@@ -19274,7 +19266,7 @@
       </c>
       <c r="F452" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0992</t>
+          <t>A-INV-EG-27-0991</t>
         </is>
       </c>
       <c r="G452" s="8" t="inlineStr"/>
@@ -19304,15 +19296,15 @@
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>Protein Shop</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E453" s="9" t="n">
-        <v>151305</v>
+        <v>275100</v>
       </c>
       <c r="F453" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0993</t>
+          <t>A-INV-EG-27-0992</t>
         </is>
       </c>
       <c r="G453" s="8" t="inlineStr"/>
@@ -19342,15 +19334,15 @@
       </c>
       <c r="D454" s="8" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>Protein Shop</t>
         </is>
       </c>
       <c r="E454" s="9" t="n">
-        <v>1236525</v>
+        <v>151305</v>
       </c>
       <c r="F454" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0994</t>
+          <t>A-INV-EG-27-0993</t>
         </is>
       </c>
       <c r="G454" s="8" t="inlineStr"/>
@@ -19380,15 +19372,15 @@
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>M/s Mayengbam Enterprises</t>
+          <t>SS Food</t>
         </is>
       </c>
       <c r="E455" s="9" t="n">
-        <v>1267341</v>
+        <v>1236525</v>
       </c>
       <c r="F455" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0995</t>
+          <t>A-INV-EG-27-0994</t>
         </is>
       </c>
       <c r="G455" s="8" t="inlineStr"/>
@@ -19418,15 +19410,15 @@
       </c>
       <c r="D456" s="8" t="inlineStr">
         <is>
-          <t>Fresh Egg Traders</t>
+          <t>M/s Mayengbam Enterprises</t>
         </is>
       </c>
       <c r="E456" s="9" t="n">
-        <v>1213191</v>
+        <v>1267341</v>
       </c>
       <c r="F456" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0996</t>
+          <t>A-INV-EG-27-0995</t>
         </is>
       </c>
       <c r="G456" s="8" t="inlineStr"/>
@@ -19451,20 +19443,20 @@
       </c>
       <c r="C457" s="8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D457" s="8" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>Fresh Egg Traders</t>
         </is>
       </c>
       <c r="E457" s="9" t="n">
-        <v>275100</v>
+        <v>1213191</v>
       </c>
       <c r="F457" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0997</t>
+          <t>A-INV-EG-27-0996</t>
         </is>
       </c>
       <c r="G457" s="8" t="inlineStr"/>
@@ -19494,15 +19486,15 @@
       </c>
       <c r="D458" s="8" t="inlineStr">
         <is>
-          <t>Josef Ali</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E458" s="9" t="n">
-        <v>184500</v>
+        <v>275100</v>
       </c>
       <c r="F458" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0998</t>
+          <t>A-INV-EG-27-0997</t>
         </is>
       </c>
       <c r="G458" s="8" t="inlineStr"/>
@@ -19532,15 +19524,15 @@
       </c>
       <c r="D459" s="8" t="inlineStr">
         <is>
-          <t>M/s Annapurna Bakery</t>
+          <t>Josef Ali</t>
         </is>
       </c>
       <c r="E459" s="9" t="n">
-        <v>60270</v>
+        <v>184500</v>
       </c>
       <c r="F459" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0999</t>
+          <t>A-INV-EG-27-0998</t>
         </is>
       </c>
       <c r="G459" s="8" t="inlineStr"/>
@@ -19570,15 +19562,15 @@
       </c>
       <c r="D460" s="8" t="inlineStr">
         <is>
-          <t>Kamakhya Traders</t>
+          <t>M/s Annapurna Bakery</t>
         </is>
       </c>
       <c r="E460" s="9" t="n">
-        <v>275100</v>
+        <v>60270</v>
       </c>
       <c r="F460" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-1000</t>
+          <t>A-INV-EG-27-0999</t>
         </is>
       </c>
       <c r="G460" s="8" t="inlineStr"/>
@@ -19608,7 +19600,7 @@
       </c>
       <c r="D461" s="8" t="inlineStr">
         <is>
-          <t>NB Traders</t>
+          <t>Kamakhya Traders</t>
         </is>
       </c>
       <c r="E461" s="9" t="n">
@@ -19616,7 +19608,7 @@
       </c>
       <c r="F461" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-1001</t>
+          <t>A-INV-EG-27-1000</t>
         </is>
       </c>
       <c r="G461" s="8" t="inlineStr"/>
@@ -19646,15 +19638,15 @@
       </c>
       <c r="D462" s="8" t="inlineStr">
         <is>
-          <t>Chowdhury n Sons</t>
+          <t>NB Traders</t>
         </is>
       </c>
       <c r="E462" s="9" t="n">
-        <v>984795</v>
+        <v>275100</v>
       </c>
       <c r="F462" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-1002</t>
+          <t>A-INV-EG-27-1001</t>
         </is>
       </c>
       <c r="G462" s="8" t="inlineStr"/>
@@ -19684,22 +19676,22 @@
       </c>
       <c r="D463" s="8" t="inlineStr">
         <is>
-          <t>Rahman Store</t>
+          <t>Chowdhury n Sons</t>
         </is>
       </c>
       <c r="E463" s="9" t="n">
-        <v>1257730</v>
+        <v>984795</v>
       </c>
       <c r="F463" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-1003</t>
+          <t>A-INV-EG-27-1002</t>
         </is>
       </c>
       <c r="G463" s="8" t="inlineStr"/>
       <c r="H463" s="8" t="inlineStr"/>
       <c r="I463" s="8" t="inlineStr">
         <is>
-          <t>overdue</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J463" s="10" t="inlineStr"/>
@@ -19722,107 +19714,101 @@
       </c>
       <c r="D464" s="8" t="inlineStr">
         <is>
-          <t>HKD Egg Traders</t>
+          <t>Rahman Store</t>
         </is>
       </c>
       <c r="E464" s="9" t="n">
-        <v>274915</v>
+        <v>1257730</v>
       </c>
       <c r="F464" s="8" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-1004</t>
+          <t>A-INV-EG-27-1003</t>
         </is>
       </c>
       <c r="G464" s="8" t="inlineStr"/>
       <c r="H464" s="8" t="inlineStr"/>
       <c r="I464" s="8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="J464" s="10" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="11" t="inlineStr">
+      <c r="A465" s="8" t="inlineStr">
+        <is>
+          <t>Only in Zoho - import</t>
+        </is>
+      </c>
+      <c r="B465" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-1030</t>
+        </is>
+      </c>
+      <c r="C465" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D465" s="8" t="inlineStr">
+        <is>
+          <t>HKD Egg Traders</t>
+        </is>
+      </c>
+      <c r="E465" s="9" t="n">
+        <v>274915</v>
+      </c>
+      <c r="F465" s="8" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-1004</t>
+        </is>
+      </c>
+      <c r="G465" s="8" t="inlineStr"/>
+      <c r="H465" s="8" t="inlineStr"/>
+      <c r="I465" s="8" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J465" s="10" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="11" t="inlineStr">
         <is>
           <t>Only in niko - keep</t>
         </is>
       </c>
-      <c r="B465" s="11" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-1030</t>
-        </is>
-      </c>
-      <c r="C465" s="11" t="inlineStr">
+      <c r="B466" s="11" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-1031</t>
+        </is>
+      </c>
+      <c r="C466" s="11" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D465" s="11" t="inlineStr">
+      <c r="D466" s="11" t="inlineStr">
         <is>
           <t>Chowdhury n Sons</t>
         </is>
       </c>
-      <c r="E465" s="12" t="n">
+      <c r="E466" s="12" t="n">
         <v>998445</v>
       </c>
-      <c r="F465" s="11" t="inlineStr"/>
-      <c r="G465" s="11" t="inlineStr">
+      <c r="F466" s="11" t="inlineStr"/>
+      <c r="G466" s="11" t="inlineStr">
         <is>
           <t>A-INV-EG-27-0858</t>
         </is>
       </c>
-      <c r="H465" s="11" t="inlineStr"/>
-      <c r="I465" s="11" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J465" s="13" t="inlineStr"/>
-    </row>
-    <row r="466">
-      <c r="A466" s="14" t="inlineStr">
-        <is>
-          <t>Figures differ - correct niko</t>
-        </is>
-      </c>
-      <c r="B466" s="14" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0307</t>
-        </is>
-      </c>
-      <c r="C466" s="14" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="D466" s="14" t="inlineStr">
-        <is>
-          <t>Aneibu Chakhesang</t>
-        </is>
-      </c>
-      <c r="E466" s="15" t="n">
-        <v>26071</v>
-      </c>
-      <c r="F466" s="14" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0307</t>
-        </is>
-      </c>
-      <c r="G466" s="14" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0307</t>
-        </is>
-      </c>
-      <c r="H466" s="15" t="n">
-        <v>39281</v>
-      </c>
-      <c r="I466" s="14" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J466" s="16" t="inlineStr"/>
+      <c r="H466" s="11" t="inlineStr"/>
+      <c r="I466" s="11" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J466" s="13" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="14" t="inlineStr">
@@ -19832,34 +19818,34 @@
       </c>
       <c r="B467" s="14" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0473</t>
+          <t>A-INV-EG-27-0211</t>
         </is>
       </c>
       <c r="C467" s="14" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D467" s="14" t="inlineStr">
         <is>
-          <t>Sahil Egg Center</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E467" s="15" t="n">
-        <v>615500</v>
+        <v>179870</v>
       </c>
       <c r="F467" s="14" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0473</t>
+          <t>A-INV-EG-27-0211</t>
         </is>
       </c>
       <c r="G467" s="14" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0473</t>
+          <t>A-INV-EG-27-0211</t>
         </is>
       </c>
       <c r="H467" s="15" t="n">
-        <v>631800</v>
+        <v>203280</v>
       </c>
       <c r="I467" s="14" t="inlineStr">
         <is>
@@ -19920,34 +19906,34 @@
       </c>
       <c r="B469" s="14" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0211</t>
+          <t>A-INV-EG-27-0473</t>
         </is>
       </c>
       <c r="C469" s="14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="D469" s="14" t="inlineStr">
         <is>
-          <t>Tapan Saha</t>
+          <t>Sahil Egg Center</t>
         </is>
       </c>
       <c r="E469" s="15" t="n">
-        <v>179870</v>
+        <v>615500</v>
       </c>
       <c r="F469" s="14" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0211</t>
+          <t>A-INV-EG-27-0473</t>
         </is>
       </c>
       <c r="G469" s="14" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0211</t>
+          <t>A-INV-EG-27-0473</t>
         </is>
       </c>
       <c r="H469" s="15" t="n">
-        <v>203280</v>
+        <v>631800</v>
       </c>
       <c r="I469" s="14" t="inlineStr">
         <is>
@@ -19957,44 +19943,48 @@
       <c r="J469" s="16" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="17" t="inlineStr">
-        <is>
-          <t>Deleted in Zoho - kept in niko</t>
-        </is>
-      </c>
-      <c r="B470" s="17" t="inlineStr"/>
-      <c r="C470" s="17" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="D470" s="17" t="inlineStr">
-        <is>
-          <t>Tapan Saha</t>
-        </is>
-      </c>
-      <c r="E470" s="18" t="n">
-        <v>273000</v>
-      </c>
-      <c r="F470" s="17" t="inlineStr"/>
-      <c r="G470" s="17" t="inlineStr">
-        <is>
-          <t>A-INV-EG-27-0779</t>
-        </is>
-      </c>
-      <c r="H470" s="18" t="n">
-        <v>273000</v>
-      </c>
-      <c r="I470" s="17" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J470" s="19" t="inlineStr">
-        <is>
-          <t>Deleted by Rohan Saraf 10 Oct; kept here by decision</t>
-        </is>
-      </c>
+      <c r="A470" s="14" t="inlineStr">
+        <is>
+          <t>Figures differ - correct niko</t>
+        </is>
+      </c>
+      <c r="B470" s="14" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0307</t>
+        </is>
+      </c>
+      <c r="C470" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D470" s="14" t="inlineStr">
+        <is>
+          <t>Aneibu Chakhesang</t>
+        </is>
+      </c>
+      <c r="E470" s="15" t="n">
+        <v>26071</v>
+      </c>
+      <c r="F470" s="14" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0307</t>
+        </is>
+      </c>
+      <c r="G470" s="14" t="inlineStr">
+        <is>
+          <t>A-INV-EG-27-0307</t>
+        </is>
+      </c>
+      <c r="H470" s="15" t="n">
+        <v>39281</v>
+      </c>
+      <c r="I470" s="14" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J470" s="16" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="17" t="inlineStr">
@@ -20005,7 +19995,7 @@
       <c r="B471" s="17" t="inlineStr"/>
       <c r="C471" s="17" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D471" s="17" t="inlineStr">
@@ -20014,16 +20004,16 @@
         </is>
       </c>
       <c r="E471" s="18" t="n">
-        <v>243600</v>
+        <v>273000</v>
       </c>
       <c r="F471" s="17" t="inlineStr"/>
       <c r="G471" s="17" t="inlineStr">
         <is>
-          <t>A-INV-EG-27-0663</t>
+          <t>A-INV-EG-27-0779</t>
         </is>
       </c>
       <c r="H471" s="18" t="n">
-        <v>243600</v>
+        <v>273000</v>
       </c>
       <c r="I471" s="17" t="inlineStr">
         <is>
@@ -20045,39 +20035,79 @@
       <c r="B472" s="17" t="inlineStr"/>
       <c r="C472" s="17" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D472" s="17" t="inlineStr">
         <is>
-          <t>SS Food</t>
+          <t>Tapan Saha</t>
         </is>
       </c>
       <c r="E472" s="18" t="n">
-        <v>4998</v>
+        <v>243600</v>
       </c>
       <c r="F472" s="17" t="inlineStr"/>
       <c r="G472" s="17" t="inlineStr">
         <is>
+          <t>A-INV-EG-27-0663</t>
+        </is>
+      </c>
+      <c r="H472" s="18" t="n">
+        <v>243600</v>
+      </c>
+      <c r="I472" s="17" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J472" s="19" t="inlineStr">
+        <is>
+          <t>Deleted by Rohan Saraf 10 Oct; kept here by decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="17" t="inlineStr">
+        <is>
+          <t>Deleted in Zoho - kept in niko</t>
+        </is>
+      </c>
+      <c r="B473" s="17" t="inlineStr"/>
+      <c r="C473" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D473" s="17" t="inlineStr">
+        <is>
+          <t>SS Food</t>
+        </is>
+      </c>
+      <c r="E473" s="18" t="n">
+        <v>4998</v>
+      </c>
+      <c r="F473" s="17" t="inlineStr"/>
+      <c r="G473" s="17" t="inlineStr">
+        <is>
           <t>A-INV-EG-27-0383</t>
         </is>
       </c>
-      <c r="H472" s="18" t="n">
+      <c r="H473" s="18" t="n">
         <v>4998</v>
       </c>
-      <c r="I472" s="17" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="J472" s="19" t="inlineStr">
+      <c r="I473" s="17" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J473" s="19" t="inlineStr">
         <is>
           <t>Deleted by Rohan Saraf 10 Oct; kept here by decision</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J472"/>
+  <autoFilter ref="A1:J473"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>